--- a/docs/PRJ301_SE20C_GROUP4 .xlsx
+++ b/docs/PRJ301_SE20C_GROUP4 .xlsx
@@ -585,7 +585,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -636,13 +636,6 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1200,134 +1193,134 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1362,25 +1355,19 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1410,10 +1397,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -1781,99 +1768,99 @@
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:5">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="31"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="29"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="31"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="29"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="31"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="29"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="31"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="29"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="31"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="29"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="31"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="29"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="31">
         <v>4</v>
       </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="31"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="29"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="31"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="29"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="31"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="29"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
@@ -1893,87 +1880,87 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="34">
+      <c r="A13" s="32">
         <v>1</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="D13" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="33" t="s">
+      <c r="E13" s="31" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="34">
+      <c r="A14" s="32">
         <v>2</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D14" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="33" t="s">
+      <c r="E14" s="31" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" ht="26.4" customHeight="1" spans="1:5">
-      <c r="A15" s="34">
+      <c r="A15" s="32">
         <v>3</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="33" t="s">
+      <c r="D15" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="33" t="s">
+      <c r="E15" s="31" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="34">
+      <c r="A16" s="32">
         <v>4</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="33" t="s">
+      <c r="E16" s="31" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="34">
+      <c r="A17" s="32">
         <v>5</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="33" t="s">
+      <c r="D17" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="33" t="s">
+      <c r="E17" s="31" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2045,98 +2032,98 @@
       </c>
     </row>
     <row r="2" ht="96" customHeight="1" spans="1:10">
-      <c r="A2" s="19">
+      <c r="A2" s="17">
         <v>1</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="20">
+      <c r="I2" s="18">
         <v>5</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="18" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="3" ht="108" customHeight="1" spans="1:10">
-      <c r="A3" s="19">
+      <c r="A3" s="17">
         <v>2</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="G3" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="H3" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="17">
         <v>4</v>
       </c>
-      <c r="J3" s="20" t="s">
+      <c r="J3" s="18" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="4" ht="115.2" customHeight="1" spans="1:10">
-      <c r="A4" s="19">
+      <c r="A4" s="17">
         <v>3</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="19">
+      <c r="I4" s="17">
         <v>4</v>
       </c>
-      <c r="J4" s="20" t="s">
+      <c r="J4" s="18" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2202,162 +2189,162 @@
       </c>
     </row>
     <row r="2" ht="121.05" customHeight="1" spans="1:10">
-      <c r="A2" s="19">
+      <c r="A2" s="17">
         <v>1</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="G2" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="20">
+      <c r="I2" s="18">
         <v>5</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="18" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="3" ht="142.95" customHeight="1" spans="1:10">
-      <c r="A3" s="19">
+      <c r="A3" s="17">
         <v>2</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="H3" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="17">
         <v>5</v>
       </c>
-      <c r="J3" s="20" t="s">
+      <c r="J3" s="18" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="4" ht="139.05" customHeight="1" spans="1:10">
-      <c r="A4" s="19">
+      <c r="A4" s="17">
         <v>3</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="19">
+      <c r="I4" s="17">
         <v>4</v>
       </c>
-      <c r="J4" s="20" t="s">
+      <c r="J4" s="18" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5" ht="187.2" customHeight="1" spans="1:10">
-      <c r="A5" s="19">
+      <c r="A5" s="17">
         <v>4</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D5" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="G5" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H5" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="I5" s="20">
+      <c r="I5" s="18">
         <v>4</v>
       </c>
-      <c r="J5" s="23" t="s">
+      <c r="J5" s="21" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="6" ht="144" customHeight="1" spans="1:10">
-      <c r="A6" s="19">
+      <c r="A6" s="17">
         <v>5</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="25" t="s">
         <v>98</v>
       </c>
       <c r="G6" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="18">
         <v>5</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="J6" s="19" t="s">
         <v>101</v>
       </c>
     </row>
@@ -2747,44 +2734,42 @@
       <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="G5" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="7">
         <v>4</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="9">
-        <v>5</v>
-      </c>
+      <c r="A6" s="9"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="18"/>
+      <c r="G6" s="16"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>

--- a/docs/PRJ301_SE20C_GROUP4 .xlsx
+++ b/docs/PRJ301_SE20C_GROUP4 .xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PRJ---24-7-LLM-Tutor\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9206C5-2F0C-4B6E-B5C2-19B068B1CE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10440" activeTab="4"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -12,7 +18,8 @@
     <sheet name="1. Week 2" sheetId="3" r:id="rId3"/>
     <sheet name="Week 4" sheetId="4" r:id="rId4"/>
     <sheet name="Week 5" sheetId="5" r:id="rId5"/>
-    <sheet name="Instruction" sheetId="6" r:id="rId6"/>
+    <sheet name="Week 6" sheetId="8" r:id="rId6"/>
+    <sheet name="Instruction" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -23,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="187">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -573,19 +578,43 @@
   </si>
   <si>
     <t>What limitations or risks you observed when using AI (e.g., “generated SQL injection-prone code”, “missing validation logic”, “incomplete test coverage”).</t>
+  </si>
+  <si>
+    <t>Implementation &amp; Security</t>
+  </si>
+  <si>
+    <t>Implement student assignment submission workflow with multipart ZIP upload, deadline enforcement, and SHA-256 file integrity hashing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Antigravity IDE, Gemini	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated boilerplate @MultipartConfig handling in SubmissionServlet.java for receiving file uploads, incrementing attempt counters (attempt_number), validating assignment deadlines, and persisting uploaded files onto the server.	</t>
+  </si>
+  <si>
+    <t>• Added security constraints: restricted maximum upload file size to 50MB and enforced strict file extension whitelisting (.zip only).
+• Integrated real-time SHA-256 checksum hashing directly from InputStream during file streaming to guarantee submission integrity.
+• Implemented automated normalized file naming convention: {courseCode}{assignmentId}{studentCode}_v{attemptNumber}.zip.
+• Enforced deadline validation logic with isOverdue() check to reject late submissions and return clear error notifications.</t>
+  </si>
+  <si>
+    <t>1 Controller (SubmissionServlet), 1 DAO (SubmissionDAO), 1 JSP (submit.jsp), 50MB file size limit, 100% SHA-256 integrity check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5	</t>
+  </si>
+  <si>
+    <t>The AI-generated code lacked file extension whitelisting and checksum calculation, posing potential arbitrary file upload risks; the team manually added .zip extension validation, a 50MB size constraint, and SHA-256 integrity verification.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1_0tZIihe4FUJd0ZMri9Jgv_lJr83gbGS?usp=sharing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00\ &quot;₫&quot;_-;\-* #,##0.00\ &quot;₫&quot;_-;_-* &quot;-&quot;??\ &quot;₫&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
-  </numFmts>
-  <fonts count="29">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -598,51 +627,51 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -650,153 +679,17 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -827,194 +720,8 @@
         <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1074,253 +781,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1343,31 +811,31 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1379,16 +847,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1397,79 +862,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1754,113 +1185,113 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.05" customHeight="1" spans="1:5">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:5" ht="28.05" customHeight="1">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="29"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="31"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="29"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="29"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="29"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="31"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="29"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="31"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="29"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="31"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="32">
         <v>4</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="29"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="31"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="29"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="31"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="29"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="31"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
@@ -1880,112 +1311,110 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="32">
+      <c r="A13" s="28">
         <v>1</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="31" t="s">
+      <c r="D13" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="E13" s="27" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="32">
+      <c r="A14" s="28">
         <v>2</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="31" t="s">
+      <c r="D14" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="27" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" ht="26.4" customHeight="1" spans="1:5">
-      <c r="A15" s="32">
+    <row r="15" spans="1:5" ht="26.4" customHeight="1">
+      <c r="A15" s="28">
         <v>3</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="31" t="s">
+      <c r="C15" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="D15" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="31" t="s">
+      <c r="E15" s="27" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="32">
+      <c r="A16" s="28">
         <v>4</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="D16" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="27" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="32">
+      <c r="A17" s="28">
         <v>5</v>
       </c>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="C17" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="D17" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="31" t="s">
+      <c r="E17" s="27" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="A11:E11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1999,7 +1428,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -2031,7 +1460,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="96" customHeight="1" spans="1:10">
+    <row r="2" spans="1:10" ht="96" customHeight="1">
       <c r="A2" s="17">
         <v>1</v>
       </c>
@@ -2050,7 +1479,7 @@
       <c r="F2" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="G2" s="25" t="s">
         <v>51</v>
       </c>
       <c r="H2" s="18" t="s">
@@ -2063,7 +1492,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" ht="108" customHeight="1" spans="1:10">
+    <row r="3" spans="1:10" ht="108" customHeight="1">
       <c r="A3" s="17">
         <v>2</v>
       </c>
@@ -2082,7 +1511,7 @@
       <c r="F3" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="25" t="s">
         <v>58</v>
       </c>
       <c r="H3" s="18" t="s">
@@ -2095,7 +1524,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" ht="115.2" customHeight="1" spans="1:10">
+    <row r="4" spans="1:10" ht="115.2" customHeight="1">
       <c r="A4" s="17">
         <v>3</v>
       </c>
@@ -2129,26 +1558,24 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link" tooltip="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link"/>
-    <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing" tooltip="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing"/>
-    <hyperlink ref="G4" r:id="rId3" display="https://drive.google.com/drive/folders/1hkfM8Mek8vMbZPqjB3AijcdotsKPLGua?usp=sharing"/>
+    <hyperlink ref="G2" r:id="rId1" tooltip="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="G3" r:id="rId2" tooltip="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="38.3333333333333" customWidth="1"/>
-    <col min="4" max="4" width="15.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="31.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="38.33203125" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="31.44140625" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
@@ -2156,7 +1583,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -2188,7 +1615,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="121.05" customHeight="1" spans="1:10">
+    <row r="2" spans="1:10" ht="121.05" customHeight="1">
       <c r="A2" s="17">
         <v>1</v>
       </c>
@@ -2220,7 +1647,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" ht="142.95" customHeight="1" spans="1:10">
+    <row r="3" spans="1:10" ht="142.94999999999999" customHeight="1">
       <c r="A3" s="17">
         <v>2</v>
       </c>
@@ -2252,7 +1679,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" ht="139.05" customHeight="1" spans="1:10">
+    <row r="4" spans="1:10" ht="139.05000000000001" customHeight="1">
       <c r="A4" s="17">
         <v>3</v>
       </c>
@@ -2284,39 +1711,39 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" ht="187.2" customHeight="1" spans="1:10">
+    <row r="5" spans="1:10" ht="187.2" customHeight="1">
       <c r="A5" s="17">
         <v>4</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="G5" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="12" t="s">
         <v>94</v>
       </c>
       <c r="I5" s="18">
         <v>4</v>
       </c>
-      <c r="J5" s="21" t="s">
+      <c r="J5" s="12" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="6" ht="144" customHeight="1" spans="1:10">
+    <row r="6" spans="1:10" ht="144" customHeight="1">
       <c r="A6" s="17">
         <v>5</v>
       </c>
@@ -2326,13 +1753,13 @@
       <c r="C6" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E6" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="24" t="s">
         <v>98</v>
       </c>
       <c r="G6" s="10" t="s">
@@ -2350,22 +1777,20 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1MvIEKYq72RDwufT_sIZ_XiyqlYSTz0PZ?usp=sharing"/>
-    <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1TsNLKc7zhuCoEUPjxf-lhVzScFA5SqKi?usp=sharing"/>
-    <hyperlink ref="G4" r:id="rId3" display="https://drive.google.com/drive/folders/1jfv8FE53NmF0-9jNc803u7VXSKQBN8MB?usp=sharing"/>
-    <hyperlink ref="G5" r:id="rId4" display="https://drive.google.com/drive/folders/1_IiKnUxj3SQwrN2uhQHVUB0enmRgof_9?usp=sharing"/>
-    <hyperlink ref="G6" r:id="rId5" display="https://drive.google.com/drive/folders/1Cv8UVkfH270j3_3KHpU-v4wu6AA63oxH?hl=vi"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2379,7 +1804,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -2411,7 +1836,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="86.4" customHeight="1" spans="1:10">
+    <row r="2" spans="1:10" ht="86.4" customHeight="1">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -2443,7 +1868,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" ht="72" customHeight="1" spans="1:10">
+    <row r="3" spans="1:10" ht="72" customHeight="1">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -2475,7 +1900,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4" ht="72" customHeight="1" spans="1:10">
+    <row r="4" spans="1:10" ht="72" customHeight="1">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -2507,7 +1932,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" ht="86.4" customHeight="1" spans="1:10">
+    <row r="5" spans="1:10" ht="86.4" customHeight="1">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -2539,7 +1964,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="6" ht="82.8" customHeight="1" spans="1:10">
+    <row r="6" spans="1:10" ht="82.8" customHeight="1">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -2573,22 +1998,20 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1Al2zQH-_4wk5DT_6O8csILsFFIXu45rO?usp=sharing"/>
-    <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1mkeoPv7QBeEjPVionr3T6jgvSR-VMuW3?usp=sharing"/>
-    <hyperlink ref="G4" r:id="rId3" display="https://drive.google.com/drive/folders/1BT8UQCi9wl8cJyHOPO71V5_QBshXmKtW?usp=sharing"/>
-    <hyperlink ref="G5" r:id="rId4" display="https://drive.google.com/drive/folders/1HDAnlKy5GQiDcsJ5ka-zU_YZRkGuqeTY?usp=sharing"/>
-    <hyperlink ref="G6" r:id="rId5" display="https://drive.google.com/drive/folders/18528q5unPQgaTq-89bPzC0Es6qiiTV2f?usp=sharing"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{00000000-0004-0000-0300-000003000000}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{00000000-0004-0000-0300-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2602,7 +2025,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -2634,7 +2057,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="110.4" customHeight="1" spans="1:10">
+    <row r="2" spans="1:10" ht="110.4" customHeight="1">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -2666,7 +2089,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="3" ht="169.95" customHeight="1" spans="1:10">
+    <row r="3" spans="1:10" ht="169.95" customHeight="1">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -2698,7 +2121,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="4" ht="82.8" spans="1:10">
+    <row r="4" spans="1:10" ht="82.8">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -2730,7 +2153,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="5" ht="82.8" spans="1:10">
+    <row r="5" spans="1:10" ht="82.8">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -2776,21 +2199,156 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1uyrqO7T6EU5SHkkqS9n9vUqZ1ghX6fXp?usp=sharing"/>
-    <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1C72WWLyzh_2zq-OIQMlprdEkDgRMdWwf?usp=sharing"/>
-    <hyperlink ref="G4" r:id="rId3" display="https://drive.google.com/drive/folders/1-OKCkuc_DCyRqRFaBMpfMPzjAfGv7iIW?usp=sharing"/>
-    <hyperlink ref="G5" r:id="rId4" display="https://drive.google.com/drive/folders/1iBfU8OXqMzE1mJFvxObm1NvyRtSjh1Ub?usp=sharing" tooltip="https://drive.google.com/drive/folders/1iBfU8OXqMzE1mJFvxObm1NvyRtSjh1Ub?usp=sharing"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
+    <hyperlink ref="G5" r:id="rId4" tooltip="https://drive.google.com/drive/folders/1iBfU8OXqMzE1mJFvxObm1NvyRtSjh1Ub?usp=sharing" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA5A9B33-B8F5-4ED2-B9BC-44B74E2C62E4}">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="30" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="220.8">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>186</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="169.95" customHeight="1">
+      <c r="A3" s="9"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="9"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="11"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="9"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="11"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="9"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{610459A8-EB3E-4B79-AE21-A33D73790B3B}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
@@ -2812,7 +2370,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="3" ht="26.4" customHeight="1" spans="1:2">
+    <row r="3" spans="1:2" ht="26.4" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>37</v>
       </c>
@@ -2820,7 +2378,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="4" ht="26.4" customHeight="1" spans="1:2">
+    <row r="4" spans="1:2" ht="26.4" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>38</v>
       </c>
@@ -2836,7 +2394,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="6" ht="26.4" customHeight="1" spans="1:2">
+    <row r="6" spans="1:2" ht="26.4" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>40</v>
       </c>
@@ -2844,7 +2402,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" ht="26.4" customHeight="1" spans="1:2">
+    <row r="7" spans="1:2" ht="26.4" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
@@ -2852,7 +2410,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="8" ht="39.6" customHeight="1" spans="1:2">
+    <row r="8" spans="1:2" ht="39.6" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>42</v>
       </c>
@@ -2860,7 +2418,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="9" ht="26.4" customHeight="1" spans="1:2">
+    <row r="9" spans="1:2" ht="26.4" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>43</v>
       </c>
@@ -2876,7 +2434,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="11" ht="26.4" customHeight="1" spans="1:2">
+    <row r="11" spans="1:2" ht="26.4" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>45</v>
       </c>
@@ -2886,6 +2444,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/docs/PRJ301_SE20C_GROUP4 .xlsx
+++ b/docs/PRJ301_SE20C_GROUP4 .xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PRJ---24-7-LLM-Tutor\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tuong Vy\Documents\GitHub\PRJ---24-7-LLM-Tutor\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9206C5-2F0C-4B6E-B5C2-19B068B1CE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970600B6-6F80-4245-A1D2-CD6BB75B0B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -22,22 +22,11 @@
     <sheet name="Instruction" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="192">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -608,13 +597,161 @@
   </si>
   <si>
     <t>https://drive.google.com/drive/folders/1_0tZIihe4FUJd0ZMri9Jgv_lJr83gbGS?usp=sharing</t>
+  </si>
+  <si>
+    <t>Full CRUD assignment lifecycle management with deadline scheduling and course/class association.</t>
+  </si>
+  <si>
+    <t>Google Antigravity IDE, Gemini</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Generated the basic CRUD structure for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>AssignmentServlet.java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>AssignmentDAO.java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1 Controller (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>AssignmentServlet.java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, 549 lines of code), 1 DAO (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>AssignmentDAO.java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, 20 KB), 3 JSP views (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>list.jsp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>form.jsp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>history.jsp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>), 4 completed CRUD operations.</t>
+    </r>
+  </si>
+  <si>
+    <t>Completed four CRUD operations: view assignment list, create new assignments (action=add), edit assignment information and extend deadlines (action=edit), and delete assignments (action=delete).
+Implemented date-time parsing from yyyy-MM-dd'T'HH:mm to SQL Timestamp.
+Added course/class-based access control: lecturers can only view and manage assignments for their assigned courses/classes, while students can only view assignments for courses they are enrolled in.
+Tested and modified the generated code to fit the project's requirements.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -687,6 +824,18 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="6">
@@ -788,7 +937,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -874,19 +1023,31 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1199,99 +1360,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.05" customHeight="1">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="31"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="32"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="32"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="32"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="32"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="32"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="32"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="30">
         <v>4</v>
       </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="32"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="32"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="31"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="32"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
@@ -2210,7 +2371,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA5A9B33-B8F5-4ED2-B9BC-44B74E2C62E4}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -2257,7 +2418,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="220.8">
+    <row r="2" spans="1:10" ht="248.4">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -2276,7 +2437,7 @@
       <c r="F2" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="G2" s="29" t="s">
         <v>186</v>
       </c>
       <c r="H2" s="7" t="s">
@@ -2289,17 +2450,29 @@
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="169.95" customHeight="1">
+    <row r="3" spans="1:10" ht="288">
       <c r="A3" s="9"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+      <c r="B3" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>187</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>188</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="F3" s="36" t="s">
+        <v>191</v>
+      </c>
       <c r="G3" s="10"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
+      <c r="J3" s="36" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="9"/>
@@ -2307,7 +2480,7 @@
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="12"/>
-      <c r="F4" s="11"/>
+      <c r="F4" s="38"/>
       <c r="G4" s="13"/>
       <c r="H4" s="11"/>
       <c r="I4" s="7"/>
@@ -2315,11 +2488,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="9"/>
-      <c r="B5" s="7"/>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="14"/>
-      <c r="F5" s="11"/>
+      <c r="F5" s="37"/>
       <c r="G5" s="15"/>
       <c r="H5" s="11"/>
       <c r="I5" s="7"/>
@@ -2331,11 +2503,20 @@
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="F6" s="38"/>
       <c r="G6" s="16"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="F7" s="37"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="F8" s="38"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="F9" s="37"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/docs/PRJ301_SE20C_GROUP4 .xlsx
+++ b/docs/PRJ301_SE20C_GROUP4 .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tuong Vy\Documents\GitHub\PRJ---24-7-LLM-Tutor\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970600B6-6F80-4245-A1D2-CD6BB75B0B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D90928CE-8069-4BBA-8BC1-D8B8DFF794C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="193">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -646,105 +646,16 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>1 Controller (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>AssignmentServlet.java</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, 549 lines of code), 1 DAO (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>AssignmentDAO.java</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, 20 KB), 3 JSP views (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>list.jsp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>form.jsp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>history.jsp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>), 4 completed CRUD operations.</t>
-    </r>
-  </si>
-  <si>
     <t>Completed four CRUD operations: view assignment list, create new assignments (action=add), edit assignment information and extend deadlines (action=edit), and delete assignments (action=delete).
 Implemented date-time parsing from yyyy-MM-dd'T'HH:mm to SQL Timestamp.
 Added course/class-based access control: lecturers can only view and manage assignments for their assigned courses/classes, while students can only view assignments for courses they are enrolled in.
 Tested and modified the generated code to fit the project's requirements.</t>
+  </si>
+  <si>
+    <t>1 Controller (AssignmentServlet.java, 549 lines of code), 1 DAO (AssignmentDAO.java, 20 KB), 3 JSP views (list.jsp, form.jsp, history.jsp), 4 completed CRUD operations.</t>
+  </si>
+  <si>
+    <t>AI-generated code may contain errors in CRUD operations, deadline parsing, and course/class access control. The team manually reviewed and tested the code to verify correct functionality and data access restrictions.</t>
   </si>
 </sst>
 </file>
@@ -2418,7 +2329,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="248.4">
+    <row r="2" spans="1:10" ht="220.8">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -2465,13 +2376,17 @@
         <v>189</v>
       </c>
       <c r="F3" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
+      <c r="I3" s="7">
+        <v>5</v>
+      </c>
       <c r="J3" s="36" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:10">

--- a/docs/PRJ301_SE20C_GROUP4 .xlsx
+++ b/docs/PRJ301_SE20C_GROUP4 .xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tuong Vy\Documents\GitHub\PRJ---24-7-LLM-Tutor\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PRJ301\PRJ---24-7-LLM-Tutor\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D90928CE-8069-4BBA-8BC1-D8B8DFF794C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C68E2FD-0C17-414B-BB65-41DE87339910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,12 @@
     <sheet name="Week 6" sheetId="8" r:id="rId6"/>
     <sheet name="Instruction" sheetId="6" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="200">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -656,6 +656,27 @@
   </si>
   <si>
     <t>AI-generated code may contain errors in CRUD operations, deadline parsing, and course/class access control. The team manually reviewed and tested the code to verify correct functionality and data access restrictions.</t>
+  </si>
+  <si>
+    <t>Architecture &amp; Security</t>
+  </si>
+  <si>
+    <t>Centralized role-based access control (RBAC AuthFilter) &amp; UTF-8 character encoding filter</t>
+  </si>
+  <si>
+    <t>Gemini, chatgpt</t>
+  </si>
+  <si>
+    <t>Created AuthFilter.java and EncodingFilter.java to protect sensitive URLs and handle Vietnamese text encoding.</t>
+  </si>
+  <si>
+    <t>Configured protected endpoints: /assignments, /submit, /grade, /user, /classes, and /learning-path. Unauthenticated users are redirected to /login?error=access_denied. Restricted students from accessing lecturer-only assignment management and grading functions. Enforced UTF-8 encoding for requests and responses.</t>
+  </si>
+  <si>
+    <t>2 filters (AuthFilter and EncodingFilter); 8+ sensitive routes targeted for protection; UTF-8 encoding applied to requests and responses.</t>
+  </si>
+  <si>
+    <t>Access-control rules and endpoint coverage must be tested. UTF-8 behavior and role permissions require validation to ensure correct operation.</t>
   </si>
 </sst>
 </file>
@@ -937,6 +958,18 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -947,18 +980,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1271,99 +1292,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.05" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="32"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="36"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="32"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="36"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="32"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="36"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="32"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="36"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="32"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="36"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="32"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="36"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="34">
         <v>4</v>
       </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="32"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="36"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="32"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="36"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="32"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="36"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
@@ -2363,19 +2384,19 @@
     </row>
     <row r="3" spans="1:10" ht="288">
       <c r="A3" s="9"/>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="31" t="s">
         <v>188</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="F3" s="36" t="s">
+      <c r="F3" s="31" t="s">
         <v>190</v>
       </c>
       <c r="G3" s="10"/>
@@ -2385,28 +2406,45 @@
       <c r="I3" s="7">
         <v>5</v>
       </c>
-      <c r="J3" s="36" t="s">
+      <c r="J3" s="31" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="9"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="38"/>
+    <row r="4" spans="1:10" ht="157.19999999999999" customHeight="1">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>197</v>
+      </c>
       <c r="G4" s="13"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="11"/>
+      <c r="H4" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="I4" s="7">
+        <v>5</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="9"/>
       <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
       <c r="E5" s="14"/>
-      <c r="F5" s="37"/>
+      <c r="F5" s="32"/>
       <c r="G5" s="15"/>
       <c r="H5" s="11"/>
       <c r="I5" s="7"/>
@@ -2416,22 +2454,21 @@
       <c r="A6" s="9"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
       <c r="E6" s="7"/>
-      <c r="F6" s="38"/>
+      <c r="F6" s="33"/>
       <c r="G6" s="16"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="F7" s="37"/>
+      <c r="F7" s="32"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="F8" s="38"/>
+      <c r="F8" s="33"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="F9" s="37"/>
+      <c r="F9" s="32"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/docs/PRJ301_SE20C_GROUP4 .xlsx
+++ b/docs/PRJ301_SE20C_GROUP4 .xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PRJ301\PRJ---24-7-LLM-Tutor\docs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C68E2FD-0C17-414B-BB65-41DE87339910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12180" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -21,12 +15,25 @@
     <sheet name="Week 6" sheetId="8" r:id="rId6"/>
     <sheet name="Instruction" sheetId="6" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="205">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -529,44 +536,6 @@
   </si>
   <si>
     <t>AI mixed business logic into the Controller; the team separated it into an independent Service layer following standard 3-tier architecture.</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>Description &amp; How to Fill</t>
-  </si>
-  <si>
-    <t>Sequential number of the log entry (1, 2, 3...).</t>
-  </si>
-  <si>
-    <t>Which phase of the project this AI usage belongs to (e.g., Requirement, Design, Implementation, Testing, Reporting).</t>
-  </si>
-  <si>
-    <t>Specific task you used AI for (e.g., Use Case Drafting, ERD Design, Servlet/JSP Coding, Test Case Generation).</t>
-  </si>
-  <si>
-    <t>Name of the AI tool (e.g., ChatGPT, GitHub Copilot, Copilot X, Bard, CodeWhisperer).</t>
-  </si>
-  <si>
-    <t>The actual output AI produced (summary only, e.g., “8 use cases generated”, “ERD with 5 entities”, “sample Servlet controller”).</t>
-  </si>
-  <si>
-    <t>How you validated or modified the AI output (e.g., “kept 6 use cases, rewrote 2”, “adjusted foreign keys”, “fixed SQL injection risk”, “refined test cases”).</t>
-  </si>
-  <si>
-    <t>Link to a shared Google Drive folder containing screenshots/videos of the AI chat session(s).
-Naming convention: GroupX_SessionY_Activity (e.g., Group5_Session2_ERD.png).
-Each screenshot/video must clearly show: prompt, AI response, and student follow-up.</t>
-  </si>
-  <si>
-    <t>Numerical evidence of the contribution (e.g., number of use cases, number of entities, number of Servlets/JSP pages, LOC, number of test cases).</t>
-  </si>
-  <si>
-    <t>Self-assessment of AI's usefulness (1 = not useful, 5 = very useful).</t>
-  </si>
-  <si>
-    <t>What limitations or risks you observed when using AI (e.g., “generated SQL injection-prone code”, “missing validation logic”, “incomplete test coverage”).</t>
   </si>
   <si>
     <t>Implementation &amp; Security</t>
@@ -587,6 +556,9 @@
 • Enforced deadline validation logic with isOverdue() check to reject late submissions and return clear error notifications.</t>
   </si>
   <si>
+    <t>https://drive.google.com/drive/folders/1_0tZIihe4FUJd0ZMri9Jgv_lJr83gbGS?usp=sharing</t>
+  </si>
+  <si>
     <t>1 Controller (SubmissionServlet), 1 DAO (SubmissionDAO), 1 JSP (submit.jsp), 50MB file size limit, 100% SHA-256 integrity check</t>
   </si>
   <si>
@@ -596,9 +568,6 @@
     <t>The AI-generated code lacked file extension whitelisting and checksum calculation, posing potential arbitrary file upload risks; the team manually added .zip extension validation, a 50MB size constraint, and SHA-256 integrity verification.</t>
   </si>
   <si>
-    <t>https://drive.google.com/drive/folders/1_0tZIihe4FUJd0ZMri9Jgv_lJr83gbGS?usp=sharing</t>
-  </si>
-  <si>
     <t>Full CRUD assignment lifecycle management with deadline scheduling and course/class association.</t>
   </si>
   <si>
@@ -606,6 +575,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">Generated the basic CRUD structure for </t>
     </r>
     <r>
@@ -613,6 +589,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
       </rPr>
       <t>AssignmentServlet.java</t>
     </r>
@@ -621,7 +598,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> and </t>
@@ -631,6 +608,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
       </rPr>
       <t>AssignmentDAO.java</t>
     </r>
@@ -639,7 +617,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
@@ -678,12 +656,76 @@
   <si>
     <t>Access-control rules and endpoint coverage must be tested. UTF-8 behavior and role permissions require validation to ensure correct operation.</t>
   </si>
+  <si>
+    <t>Lecturer submission review table, ZIP file download stream, and AJAX-based grading modal with score &amp; feedback</t>
+  </si>
+  <si>
+    <t>Generated the GradeServlet.java servlet and the submissions.jsp interface, allowing lecturers to view the list of students who have submitted assignments and grade their work.</t>
+  </si>
+  <si>
+    <t>onverted the grading mechanism to use AJAX POST /grade, returning JSON instead of reloading the page. Scores and feedback are updated immediately in the table.
+Implemented strict access control, allowing only users with the Instructor or Admin role to access the grading functionality. Student accounts are immediately blocked with a 403 Forbidden error.
+Implemented direct ZIP file downloads for students' submitted assignments using the stored file paths.</t>
+  </si>
+  <si>
+    <t>1 Controller (GradeServlet), 1 JSP view (submissions.jsp), 1 AJAX REST API endpoint (/grade), and 100% role-based access control coverage.</t>
+  </si>
+  <si>
+    <t>Unauthorized access may occur if role-based access control is not properly implemented.
+Invalid input or server errors may cause grading requests to fail.
+ZIP file downloads may fail if the stored file path is incorrect or the file is missing.
+AJAX requests require proper error handling to ensure users receive clear feedback when grading fails.</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>Description &amp; How to Fill</t>
+  </si>
+  <si>
+    <t>Sequential number of the log entry (1, 2, 3...).</t>
+  </si>
+  <si>
+    <t>Which phase of the project this AI usage belongs to (e.g., Requirement, Design, Implementation, Testing, Reporting).</t>
+  </si>
+  <si>
+    <t>Specific task you used AI for (e.g., Use Case Drafting, ERD Design, Servlet/JSP Coding, Test Case Generation).</t>
+  </si>
+  <si>
+    <t>Name of the AI tool (e.g., ChatGPT, GitHub Copilot, Copilot X, Bard, CodeWhisperer).</t>
+  </si>
+  <si>
+    <t>The actual output AI produced (summary only, e.g., “8 use cases generated”, “ERD with 5 entities”, “sample Servlet controller”).</t>
+  </si>
+  <si>
+    <t>How you validated or modified the AI output (e.g., “kept 6 use cases, rewrote 2”, “adjusted foreign keys”, “fixed SQL injection risk”, “refined test cases”).</t>
+  </si>
+  <si>
+    <t>Link to a shared Google Drive folder containing screenshots/videos of the AI chat session(s).
+Naming convention: GroupX_SessionY_Activity (e.g., Group5_Session2_ERD.png).
+Each screenshot/video must clearly show: prompt, AI response, and student follow-up.</t>
+  </si>
+  <si>
+    <t>Numerical evidence of the contribution (e.g., number of use cases, number of entities, number of Servlets/JSP pages, LOC, number of test cases).</t>
+  </si>
+  <si>
+    <t>Self-assessment of AI's usefulness (1 = not useful, 5 = very useful).</t>
+  </si>
+  <si>
+    <t>What limitations or risks you observed when using AI (e.g., “generated SQL injection-prone code”, “missing validation logic”, “incomplete test coverage”).</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -696,51 +738,58 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -748,29 +797,159 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -801,8 +980,194 @@
         <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -862,14 +1227,253 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -892,49 +1496,73 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -943,57 +1571,79 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1278,21 +1928,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.05" customHeight="1">
-      <c r="A1" s="38" t="s">
+    <row r="1" ht="28.05" customHeight="1" spans="1:5">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="35"/>
@@ -1301,10 +1951,10 @@
       <c r="E1" s="36"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="38" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="35"/>
@@ -1312,10 +1962,10 @@
       <c r="E3" s="36"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="38" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="35"/>
@@ -1323,10 +1973,10 @@
       <c r="E4" s="36"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="38" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="35"/>
@@ -1334,10 +1984,10 @@
       <c r="E5" s="36"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="38" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="35"/>
@@ -1345,10 +1995,10 @@
       <c r="E6" s="36"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="38" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="35"/>
@@ -1356,10 +2006,10 @@
       <c r="E7" s="36"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="38">
         <v>4</v>
       </c>
       <c r="C8" s="35"/>
@@ -1367,10 +2017,10 @@
       <c r="E8" s="36"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="35"/>
@@ -1404,110 +2054,112 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="28">
+      <c r="A13" s="39">
         <v>1</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="27" t="s">
+      <c r="E13" s="38" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="28">
+      <c r="A14" s="39">
         <v>2</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="38" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="26.4" customHeight="1">
-      <c r="A15" s="28">
+    <row r="15" ht="26.4" customHeight="1" spans="1:5">
+      <c r="A15" s="39">
         <v>3</v>
       </c>
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="E15" s="38" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="28">
+      <c r="A16" s="39">
         <v>4</v>
       </c>
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="27" t="s">
+      <c r="E16" s="38" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="28">
+      <c r="A17" s="39">
         <v>5</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="38" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A11:E11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1521,7 +2173,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1">
+    <row r="1" ht="30" customHeight="1" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -1553,122 +2205,124 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="96" customHeight="1">
-      <c r="A2" s="17">
+    <row r="2" ht="96" customHeight="1" spans="1:10">
+      <c r="A2" s="13">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="18">
+      <c r="I2" s="14">
         <v>5</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="14" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="108" customHeight="1">
-      <c r="A3" s="17">
+    <row r="3" ht="108" customHeight="1" spans="1:10">
+      <c r="A3" s="13">
         <v>2</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="G3" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="13">
         <v>4</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="J3" s="14" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="115.2" customHeight="1">
-      <c r="A4" s="17">
+    <row r="4" ht="115.2" customHeight="1" spans="1:10">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="17">
+      <c r="I4" s="13">
         <v>4</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="14" t="s">
         <v>68</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" tooltip="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="G3" r:id="rId2" tooltip="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link" tooltip="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing" tooltip="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing"/>
+    <hyperlink ref="G4" r:id="rId3" display="https://drive.google.com/drive/folders/1hkfM8Mek8vMbZPqjB3AijcdotsKPLGua?usp=sharing"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="38.33203125" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" customWidth="1"/>
-    <col min="5" max="5" width="31.44140625" customWidth="1"/>
+    <col min="3" max="3" width="38.3333333333333" customWidth="1"/>
+    <col min="4" max="4" width="15.552380952381" customWidth="1"/>
+    <col min="5" max="5" width="31.4380952380952" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
@@ -1676,7 +2330,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1">
+    <row r="1" ht="30" customHeight="1" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -1708,182 +2362,184 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="121.05" customHeight="1">
-      <c r="A2" s="17">
+    <row r="2" ht="121.05" customHeight="1" spans="1:10">
+      <c r="A2" s="13">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="18">
+      <c r="I2" s="14">
         <v>5</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="142.94999999999999" customHeight="1">
-      <c r="A3" s="17">
+    <row r="3" ht="142.95" customHeight="1" spans="1:10">
+      <c r="A3" s="13">
         <v>2</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="13">
         <v>5</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="J3" s="14" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="139.05000000000001" customHeight="1">
-      <c r="A4" s="17">
+    <row r="4" ht="139.05" customHeight="1" spans="1:10">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="17">
+      <c r="I4" s="13">
         <v>4</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="14" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="187.2" customHeight="1">
-      <c r="A5" s="17">
+    <row r="5" ht="187.2" customHeight="1" spans="1:10">
+      <c r="A5" s="13">
         <v>4</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="14">
         <v>4</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="25" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="144" customHeight="1">
-      <c r="A6" s="17">
+    <row r="6" ht="144" customHeight="1" spans="1:10">
+      <c r="A6" s="13">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F6" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="14">
         <v>5</v>
       </c>
-      <c r="J6" s="19" t="s">
+      <c r="J6" s="27" t="s">
         <v>101</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="G3" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
-    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
-    <hyperlink ref="G5" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
-    <hyperlink ref="G6" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
+    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1MvIEKYq72RDwufT_sIZ_XiyqlYSTz0PZ?usp=sharing"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1TsNLKc7zhuCoEUPjxf-lhVzScFA5SqKi?usp=sharing"/>
+    <hyperlink ref="G4" r:id="rId3" display="https://drive.google.com/drive/folders/1jfv8FE53NmF0-9jNc803u7VXSKQBN8MB?usp=sharing"/>
+    <hyperlink ref="G5" r:id="rId4" display="https://drive.google.com/drive/folders/1_IiKnUxj3SQwrN2uhQHVUB0enmRgof_9?usp=sharing"/>
+    <hyperlink ref="G6" r:id="rId5" display="https://drive.google.com/drive/folders/1Cv8UVkfH270j3_3KHpU-v4wu6AA63oxH?hl=vi"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1897,7 +2553,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1">
+    <row r="1" ht="30" customHeight="1" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -1929,7 +2585,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="86.4" customHeight="1">
+    <row r="2" ht="86.4" customHeight="1" spans="1:10">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -1948,7 +2604,7 @@
       <c r="F2" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="24" t="s">
         <v>106</v>
       </c>
       <c r="H2" s="7" t="s">
@@ -1961,7 +2617,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="72" customHeight="1">
+    <row r="3" ht="72" customHeight="1" spans="1:10">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -1980,7 +2636,7 @@
       <c r="F3" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="24" t="s">
         <v>113</v>
       </c>
       <c r="H3" s="7" t="s">
@@ -1993,7 +2649,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="72" customHeight="1">
+    <row r="4" ht="72" customHeight="1" spans="1:10">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -2012,7 +2668,7 @@
       <c r="F4" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="24" t="s">
         <v>120</v>
       </c>
       <c r="H4" s="7" t="s">
@@ -2025,7 +2681,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="86.4" customHeight="1">
+    <row r="5" ht="86.4" customHeight="1" spans="1:10">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -2044,7 +2700,7 @@
       <c r="F5" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="24" t="s">
         <v>126</v>
       </c>
       <c r="H5" s="7" t="s">
@@ -2057,7 +2713,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="82.8" customHeight="1">
+    <row r="6" ht="82.8" customHeight="1" spans="1:10">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -2076,7 +2732,7 @@
       <c r="F6" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="24" t="s">
         <v>133</v>
       </c>
       <c r="H6" s="7" t="s">
@@ -2091,20 +2747,22 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
-    <hyperlink ref="G3" r:id="rId2" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
-    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
-    <hyperlink ref="G5" r:id="rId4" xr:uid="{00000000-0004-0000-0300-000003000000}"/>
-    <hyperlink ref="G6" r:id="rId5" xr:uid="{00000000-0004-0000-0300-000004000000}"/>
+    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1Al2zQH-_4wk5DT_6O8csILsFFIXu45rO?usp=sharing"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1mkeoPv7QBeEjPVionr3T6jgvSR-VMuW3?usp=sharing"/>
+    <hyperlink ref="G4" r:id="rId3" display="https://drive.google.com/drive/folders/1BT8UQCi9wl8cJyHOPO71V5_QBshXmKtW?usp=sharing"/>
+    <hyperlink ref="G5" r:id="rId4" display="https://drive.google.com/drive/folders/1HDAnlKy5GQiDcsJ5ka-zU_YZRkGuqeTY?usp=sharing"/>
+    <hyperlink ref="G6" r:id="rId5" display="https://drive.google.com/drive/folders/18528q5unPQgaTq-89bPzC0Es6qiiTV2f?usp=sharing"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2118,7 +2776,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1">
+    <row r="1" ht="30" customHeight="1" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -2150,7 +2808,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="110.4" customHeight="1">
+    <row r="2" ht="110.4" customHeight="1" spans="1:10">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -2169,7 +2827,7 @@
       <c r="F2" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="24" t="s">
         <v>141</v>
       </c>
       <c r="H2" s="7" t="s">
@@ -2182,7 +2840,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="169.95" customHeight="1">
+    <row r="3" ht="169.95" customHeight="1" spans="1:10">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -2201,7 +2859,7 @@
       <c r="F3" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="12" t="s">
         <v>148</v>
       </c>
       <c r="H3" s="7" t="s">
@@ -2214,67 +2872,67 @@
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="82.8">
+    <row r="4" ht="90" spans="1:10">
       <c r="A4" s="9">
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="21" t="s">
         <v>156</v>
       </c>
       <c r="I4" s="7">
         <v>5</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="21" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="82.8">
+    <row r="5" ht="99.75" spans="1:10">
       <c r="A5" s="9">
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="21" t="s">
         <v>164</v>
       </c>
       <c r="I5" s="7">
         <v>4</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="21" t="s">
         <v>165</v>
       </c>
     </row>
@@ -2285,26 +2943,28 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="16"/>
+      <c r="G6" s="23"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
-    <hyperlink ref="G3" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
-    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
-    <hyperlink ref="G5" r:id="rId4" tooltip="https://drive.google.com/drive/folders/1iBfU8OXqMzE1mJFvxObm1NvyRtSjh1Ub?usp=sharing" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
+    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1uyrqO7T6EU5SHkkqS9n9vUqZ1ghX6fXp?usp=sharing"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1C72WWLyzh_2zq-OIQMlprdEkDgRMdWwf?usp=sharing"/>
+    <hyperlink ref="G4" r:id="rId3" display="https://drive.google.com/drive/folders/1-OKCkuc_DCyRqRFaBMpfMPzjAfGv7iIW?usp=sharing"/>
+    <hyperlink ref="G5" r:id="rId4" display="https://drive.google.com/drive/folders/1iBfU8OXqMzE1mJFvxObm1NvyRtSjh1Ub?usp=sharing" tooltip="https://drive.google.com/drive/folders/1iBfU8OXqMzE1mJFvxObm1NvyRtSjh1Ub?usp=sharing"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA5A9B33-B8F5-4ED2-B9BC-44B74E2C62E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2318,7 +2978,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1">
+    <row r="1" ht="30" customHeight="1" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -2350,138 +3010,160 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="220.8">
+    <row r="2" ht="270" spans="1:10">
       <c r="A2" s="6">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" ht="315" spans="1:10">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="F3" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="G3" s="12"/>
+      <c r="H3" s="7" t="s">
         <v>179</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="G2" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="288">
-      <c r="A3" s="9"/>
-      <c r="B3" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="31" t="s">
-        <v>187</v>
-      </c>
-      <c r="D3" s="31" t="s">
-        <v>188</v>
-      </c>
-      <c r="E3" s="31" t="s">
-        <v>189</v>
-      </c>
-      <c r="F3" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="7" t="s">
-        <v>191</v>
       </c>
       <c r="I3" s="7">
         <v>5</v>
       </c>
-      <c r="J3" s="31" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="157.19999999999999" customHeight="1">
+      <c r="J3" s="11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" ht="157.2" customHeight="1" spans="1:10">
       <c r="A4" s="9">
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="G4" s="13"/>
+        <v>182</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="G4" s="15"/>
       <c r="H4" s="7" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="I4" s="7">
         <v>5</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="9"/>
-      <c r="C5" s="11"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="11"/>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" ht="168" customHeight="1" spans="1:10">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="G5" s="20"/>
+      <c r="H5" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="I5" s="7">
+        <v>5</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="9"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="E6" s="7"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="16"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="23"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="F7" s="32"/>
+      <c r="F7" s="19"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="F8" s="33"/>
+      <c r="F8" s="22"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="F9" s="32"/>
+      <c r="F9" s="19"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{610459A8-EB3E-4B79-AE21-A33D73790B3B}"/>
+    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1_0tZIihe4FUJd0ZMri9Jgv_lJr83gbGS?usp=sharing"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
@@ -2489,10 +3171,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2500,23 +3182,23 @@
         <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="26.4" customHeight="1">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="3" ht="26.4" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="26.4" customHeight="1">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4" ht="26.4" customHeight="1" spans="1:2">
       <c r="A4" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2524,39 +3206,39 @@
         <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="26.4" customHeight="1">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="6" ht="26.4" customHeight="1" spans="1:2">
       <c r="A6" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="26.4" customHeight="1">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="7" ht="26.4" customHeight="1" spans="1:2">
       <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="39.6" customHeight="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" ht="39.6" customHeight="1" spans="1:2">
       <c r="A8" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="26.4" customHeight="1">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="9" ht="26.4" customHeight="1" spans="1:2">
       <c r="A9" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2564,18 +3246,19 @@
         <v>44</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="26.4" customHeight="1">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="11" ht="26.4" customHeight="1" spans="1:2">
       <c r="A11" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/docs/PRJ301_SE20C_GROUP4 .xlsx
+++ b/docs/PRJ301_SE20C_GROUP4 .xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" activeTab="5"/>
+    <workbookView windowWidth="22188" windowHeight="10440" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="208">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -556,7 +556,7 @@
 • Enforced deadline validation logic with isOverdue() check to reject late submissions and return clear error notifications.</t>
   </si>
   <si>
-    <t>https://drive.google.com/drive/folders/1_0tZIihe4FUJd0ZMri9Jgv_lJr83gbGS?usp=sharing</t>
+    <t>https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/cf570a4</t>
   </si>
   <si>
     <t>1 Controller (SubmissionServlet), 1 DAO (SubmissionDAO), 1 JSP (submit.jsp), 50MB file size limit, 100% SHA-256 integrity check</t>
@@ -630,6 +630,9 @@
 Tested and modified the generated code to fit the project's requirements.</t>
   </si>
   <si>
+    <t>https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/3901ac5</t>
+  </si>
+  <si>
     <t>1 Controller (AssignmentServlet.java, 549 lines of code), 1 DAO (AssignmentDAO.java, 20 KB), 3 JSP views (list.jsp, form.jsp, history.jsp), 4 completed CRUD operations.</t>
   </si>
   <si>
@@ -649,6 +652,9 @@
   </si>
   <si>
     <t>Configured protected endpoints: /assignments, /submit, /grade, /user, /classes, and /learning-path. Unauthenticated users are redirected to /login?error=access_denied. Restricted students from accessing lecturer-only assignment management and grading functions. Enforced UTF-8 encoding for requests and responses.</t>
+  </si>
+  <si>
+    <t>https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/12eb884</t>
   </si>
   <si>
     <t>2 filters (AuthFilter and EncodingFilter); 8+ sensitive routes targeted for protection; UTF-8 encoding applied to requests and responses.</t>
@@ -666,6 +672,9 @@
     <t>onverted the grading mechanism to use AJAX POST /grade, returning JSON instead of reloading the page. Scores and feedback are updated immediately in the table.
 Implemented strict access control, allowing only users with the Instructor or Admin role to access the grading functionality. Student accounts are immediately blocked with a 403 Forbidden error.
 Implemented direct ZIP file downloads for students' submitted assignments using the stored file paths.</t>
+  </si>
+  <si>
+    <t>https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/fb3e135</t>
   </si>
   <si>
     <t>1 Controller (GradeServlet), 1 JSP view (submissions.jsp), 1 AJAX REST API endpoint (/grade), and 100% role-based access control coverage.</t>
@@ -720,12 +729,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -776,13 +785,6 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1331,149 +1333,149 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1502,56 +1504,53 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1566,15 +1565,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -1935,106 +1931,106 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:5">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="36"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="34"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="36"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="34"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="36"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="34"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="36"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="34"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="36"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="34"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="36"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="34"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="38">
+      <c r="B8" s="36">
         <v>4</v>
       </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="36"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="34"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="36"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="34"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="36"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
@@ -2054,87 +2050,87 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="39">
+      <c r="A13" s="37">
         <v>1</v>
       </c>
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="38" t="s">
+      <c r="C13" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="38" t="s">
+      <c r="D13" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="38" t="s">
+      <c r="E13" s="36" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="39">
+      <c r="A14" s="37">
         <v>2</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="38" t="s">
+      <c r="E14" s="36" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" ht="26.4" customHeight="1" spans="1:5">
-      <c r="A15" s="39">
+      <c r="A15" s="37">
         <v>3</v>
       </c>
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="38" t="s">
+      <c r="C15" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="38" t="s">
+      <c r="D15" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="38" t="s">
+      <c r="E15" s="36" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="39">
+      <c r="A16" s="37">
         <v>4</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="C16" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="38" t="s">
+      <c r="D16" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="38" t="s">
+      <c r="E16" s="36" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="39">
+      <c r="A17" s="37">
         <v>5</v>
       </c>
-      <c r="B17" s="38" t="s">
+      <c r="B17" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="38" t="s">
+      <c r="C17" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="38" t="s">
+      <c r="D17" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="38" t="s">
+      <c r="E17" s="36" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2159,7 +2155,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2206,98 +2202,98 @@
       </c>
     </row>
     <row r="2" ht="96" customHeight="1" spans="1:10">
-      <c r="A2" s="13">
+      <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="33" t="s">
+      <c r="G2" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="13">
         <v>5</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="13" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="3" ht="108" customHeight="1" spans="1:10">
-      <c r="A3" s="13">
+      <c r="A3" s="12">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="33" t="s">
+      <c r="G3" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="13">
+      <c r="I3" s="12">
         <v>4</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="13" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="4" ht="115.2" customHeight="1" spans="1:10">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="12">
         <v>4</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="13" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2316,13 +2312,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="38.3333333333333" customWidth="1"/>
-    <col min="4" max="4" width="15.552380952381" customWidth="1"/>
-    <col min="5" max="5" width="31.4380952380952" customWidth="1"/>
+    <col min="4" max="4" width="15.5555555555556" customWidth="1"/>
+    <col min="5" max="5" width="31.4351851851852" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
@@ -2363,162 +2359,162 @@
       </c>
     </row>
     <row r="2" ht="121.05" customHeight="1" spans="1:10">
-      <c r="A2" s="13">
+      <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="13">
         <v>5</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="13" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="3" ht="142.95" customHeight="1" spans="1:10">
-      <c r="A3" s="13">
+      <c r="A3" s="12">
         <v>2</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="G3" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="I3" s="13">
+      <c r="I3" s="12">
         <v>5</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="13" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="4" ht="139.05" customHeight="1" spans="1:10">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="12">
         <v>4</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="13" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5" ht="187.2" customHeight="1" spans="1:10">
-      <c r="A5" s="13">
+      <c r="A5" s="12">
         <v>4</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="G5" s="30" t="s">
+      <c r="G5" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="H5" s="25" t="s">
+      <c r="H5" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="13">
         <v>4</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="22" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="6" ht="144" customHeight="1" spans="1:10">
-      <c r="A6" s="13">
+      <c r="A6" s="12">
         <v>5</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="F6" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H6" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="13">
         <v>5</v>
       </c>
-      <c r="J6" s="27" t="s">
+      <c r="J6" s="26" t="s">
         <v>101</v>
       </c>
     </row>
@@ -2539,7 +2535,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2604,7 +2600,7 @@
       <c r="F2" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="G2" s="20" t="s">
         <v>106</v>
       </c>
       <c r="H2" s="7" t="s">
@@ -2636,7 +2632,7 @@
       <c r="F3" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="20" t="s">
         <v>113</v>
       </c>
       <c r="H3" s="7" t="s">
@@ -2668,7 +2664,7 @@
       <c r="F4" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="20" t="s">
         <v>120</v>
       </c>
       <c r="H4" s="7" t="s">
@@ -2700,7 +2696,7 @@
       <c r="F5" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="G5" s="20" t="s">
         <v>126</v>
       </c>
       <c r="H5" s="7" t="s">
@@ -2732,7 +2728,7 @@
       <c r="F6" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="G6" s="20" t="s">
         <v>133</v>
       </c>
       <c r="H6" s="7" t="s">
@@ -2762,7 +2758,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2827,7 +2823,7 @@
       <c r="F2" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="G2" s="20" t="s">
         <v>141</v>
       </c>
       <c r="H2" s="7" t="s">
@@ -2859,7 +2855,7 @@
       <c r="F3" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="21" t="s">
         <v>148</v>
       </c>
       <c r="H3" s="7" t="s">
@@ -2872,67 +2868,67 @@
         <v>150</v>
       </c>
     </row>
-    <row r="4" ht="90" spans="1:10">
+    <row r="4" ht="82.8" spans="1:10">
       <c r="A4" s="9">
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="17" t="s">
         <v>156</v>
       </c>
       <c r="I4" s="7">
         <v>5</v>
       </c>
-      <c r="J4" s="21" t="s">
+      <c r="J4" s="17" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="5" ht="99.75" spans="1:10">
+    <row r="5" ht="82.8" spans="1:10">
       <c r="A5" s="9">
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="17" t="s">
         <v>164</v>
       </c>
       <c r="I5" s="7">
         <v>4</v>
       </c>
-      <c r="J5" s="21" t="s">
+      <c r="J5" s="17" t="s">
         <v>165</v>
       </c>
     </row>
@@ -2943,7 +2939,7 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="23"/>
+      <c r="G6" s="19"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -2964,18 +2960,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="26" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="5" max="5" width="34.8888888888889" customWidth="1"/>
+    <col min="6" max="6" width="75" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="26" customWidth="1"/>
+    <col min="8" max="8" width="32.4444444444444" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="61.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:10">
@@ -3010,7 +3006,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="270" spans="1:10">
+    <row r="2" ht="220.8" spans="1:10">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -3042,7 +3038,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="3" ht="315" spans="1:10">
+    <row r="3" ht="259.2" spans="1:10">
       <c r="A3" s="9"/>
       <c r="B3" s="10" t="s">
         <v>54</v>
@@ -3059,15 +3055,17 @@
       <c r="F3" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="G3" s="12"/>
+      <c r="G3" s="8" t="s">
+        <v>179</v>
+      </c>
       <c r="H3" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I3" s="7">
         <v>5</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" ht="157.2" customHeight="1" spans="1:10">
@@ -3075,59 +3073,63 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="D4" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="D4" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="E4" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="G4" s="15"/>
+      <c r="F4" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>187</v>
+      </c>
       <c r="H4" s="7" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I4" s="7">
         <v>5</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" ht="168" customHeight="1" spans="1:10">
       <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="D5" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="D5" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="E5" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="G5" s="20"/>
-      <c r="H5" s="21" t="s">
+      <c r="E5" s="15" t="s">
         <v>191</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>194</v>
       </c>
       <c r="I5" s="7">
         <v>5</v>
       </c>
-      <c r="J5" s="21" t="s">
-        <v>192</v>
+      <c r="J5" s="17" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3135,24 +3137,27 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="E6" s="7"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="23"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="19"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="F7" s="19"/>
+      <c r="F7" s="16"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="F8" s="22"/>
+      <c r="F8" s="18"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="F9" s="19"/>
+      <c r="F9" s="16"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1_0tZIihe4FUJd0ZMri9Jgv_lJr83gbGS?usp=sharing"/>
+    <hyperlink ref="G2" r:id="rId1" display="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/cf570a4" tooltip="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/cf570a4"/>
+    <hyperlink ref="G5" r:id="rId2" display="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/fb3e135"/>
+    <hyperlink ref="G4" r:id="rId3" display="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/12eb884"/>
+    <hyperlink ref="G3" r:id="rId4" display="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/3901ac5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -3163,7 +3168,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
@@ -3171,10 +3176,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -3182,7 +3187,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" ht="26.4" customHeight="1" spans="1:2">
@@ -3190,7 +3195,7 @@
         <v>37</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" ht="26.4" customHeight="1" spans="1:2">
@@ -3198,7 +3203,7 @@
         <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3206,7 +3211,7 @@
         <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" ht="26.4" customHeight="1" spans="1:2">
@@ -3214,7 +3219,7 @@
         <v>40</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" ht="26.4" customHeight="1" spans="1:2">
@@ -3222,7 +3227,7 @@
         <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" ht="39.6" customHeight="1" spans="1:2">
@@ -3230,7 +3235,7 @@
         <v>42</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" ht="26.4" customHeight="1" spans="1:2">
@@ -3238,7 +3243,7 @@
         <v>43</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3246,7 +3251,7 @@
         <v>44</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" ht="26.4" customHeight="1" spans="1:2">
@@ -3254,7 +3259,7 @@
         <v>45</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/docs/PRJ301_SE20C_GROUP4 .xlsx
+++ b/docs/PRJ301_SE20C_GROUP4 .xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10440" activeTab="5"/>
+    <workbookView windowWidth="22188" windowHeight="10440" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,8 @@
     <sheet name="Week 4" sheetId="4" r:id="rId4"/>
     <sheet name="Week 5" sheetId="5" r:id="rId5"/>
     <sheet name="Week 6" sheetId="8" r:id="rId6"/>
-    <sheet name="Instruction" sheetId="6" r:id="rId7"/>
+    <sheet name="Week 7" sheetId="10" r:id="rId7"/>
+    <sheet name="Instruction" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="216">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -684,6 +685,30 @@
 Invalid input or server errors may cause grading requests to fail.
 ZIP file downloads may fail if the stored file path is incorrect or the file is missing.
 AJAX requests require proper error handling to ensure users receive clear feedback when grading fails.</t>
+  </si>
+  <si>
+    <t>Implementation &amp; Integration</t>
+  </si>
+  <si>
+    <t>Implement AI Tutor Chatbot integration with Gemini and OpenAI for real-time programming support.</t>
+  </si>
+  <si>
+    <t>Gemini, ChatGPT/Codex/antigravity</t>
+  </si>
+  <si>
+    <t>Generated/refined the ChatServlet and AiTutorService structure for sending student questions to an LLM provider, handling API responses, and returning JSON to the chat interface.</t>
+  </si>
+  <si>
+    <t>Modification Reviewed and integrated the AI-generated code into the Java Web project. Kept API keys on the server side, added validation for empty and oversized messages, configured connection/read timeouts, handled network/quota/authentication errors, and implemented Gemini-to-OpenAI fallback when Gemini is unavailable.</t>
+  </si>
+  <si>
+    <t>https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/2584cd05cdc1b59d1bc66b29b55425e534f5034d</t>
+  </si>
+  <si>
+    <t>1 ChatServlet; 1 AiTutorService; 2 AI providers (Gemini and OpenAI); maximum 30,000 characters per message; up to 40 recent messages used as conversation context.</t>
+  </si>
+  <si>
+    <t>AI response quality depends on the selected model and prompt. External API calls can fail because of missing API keys, network timeouts, quota limits, or provider outages. Live API behavior must be tested with valid credentials.</t>
   </si>
   <si>
     <t>Column</t>
@@ -1475,7 +1500,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1509,6 +1534,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1938,99 +1966,99 @@
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:5">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="34"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="35"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="35"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="35"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="35"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="35"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="35"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="36">
+      <c r="B8" s="37">
         <v>4</v>
       </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="35"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="35"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="34"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="35"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
@@ -2050,87 +2078,87 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="37">
+      <c r="A13" s="38">
         <v>1</v>
       </c>
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="36" t="s">
+      <c r="D13" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="36" t="s">
+      <c r="E13" s="37" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="37">
+      <c r="A14" s="38">
         <v>2</v>
       </c>
-      <c r="B14" s="36" t="s">
+      <c r="B14" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="C14" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="36" t="s">
+      <c r="D14" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="36" t="s">
+      <c r="E14" s="37" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" ht="26.4" customHeight="1" spans="1:5">
-      <c r="A15" s="37">
+      <c r="A15" s="38">
         <v>3</v>
       </c>
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="36" t="s">
+      <c r="D15" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="36" t="s">
+      <c r="E15" s="37" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="37">
+      <c r="A16" s="38">
         <v>4</v>
       </c>
-      <c r="B16" s="36" t="s">
+      <c r="B16" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="36" t="s">
+      <c r="C16" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="36" t="s">
+      <c r="D16" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="36" t="s">
+      <c r="E16" s="37" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="37">
+      <c r="A17" s="38">
         <v>5</v>
       </c>
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="36" t="s">
+      <c r="D17" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="36" t="s">
+      <c r="E17" s="37" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2202,98 +2230,98 @@
       </c>
     </row>
     <row r="2" ht="96" customHeight="1" spans="1:10">
-      <c r="A2" s="12">
+      <c r="A2" s="13">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="14">
         <v>5</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="14" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="3" ht="108" customHeight="1" spans="1:10">
-      <c r="A3" s="12">
+      <c r="A3" s="13">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="13">
         <v>4</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="14" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="4" ht="115.2" customHeight="1" spans="1:10">
-      <c r="A4" s="12">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="27" t="s">
+      <c r="G4" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="13">
         <v>4</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="14" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2359,162 +2387,162 @@
       </c>
     </row>
     <row r="2" ht="121.05" customHeight="1" spans="1:10">
-      <c r="A2" s="12">
+      <c r="A2" s="13">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="14">
         <v>5</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="14" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="3" ht="142.95" customHeight="1" spans="1:10">
-      <c r="A3" s="12">
+      <c r="A3" s="13">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="13">
         <v>5</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="14" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="4" ht="139.05" customHeight="1" spans="1:10">
-      <c r="A4" s="12">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="G4" s="27" t="s">
+      <c r="G4" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="13">
         <v>4</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5" ht="187.2" customHeight="1" spans="1:10">
-      <c r="A5" s="12">
+      <c r="A5" s="13">
         <v>4</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G5" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="14">
         <v>4</v>
       </c>
-      <c r="J5" s="22" t="s">
+      <c r="J5" s="23" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="6" ht="144" customHeight="1" spans="1:10">
-      <c r="A6" s="12">
+      <c r="A6" s="13">
         <v>5</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="H6" s="26" t="s">
+      <c r="H6" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="14">
         <v>5</v>
       </c>
-      <c r="J6" s="26" t="s">
+      <c r="J6" s="27" t="s">
         <v>101</v>
       </c>
     </row>
@@ -2600,7 +2628,7 @@
       <c r="F2" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>106</v>
       </c>
       <c r="H2" s="7" t="s">
@@ -2632,7 +2660,7 @@
       <c r="F3" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="21" t="s">
         <v>113</v>
       </c>
       <c r="H3" s="7" t="s">
@@ -2664,7 +2692,7 @@
       <c r="F4" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="21" t="s">
         <v>120</v>
       </c>
       <c r="H4" s="7" t="s">
@@ -2696,7 +2724,7 @@
       <c r="F5" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="21" t="s">
         <v>126</v>
       </c>
       <c r="H5" s="7" t="s">
@@ -2728,7 +2756,7 @@
       <c r="F6" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="21" t="s">
         <v>133</v>
       </c>
       <c r="H6" s="7" t="s">
@@ -2823,7 +2851,7 @@
       <c r="F2" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>141</v>
       </c>
       <c r="H2" s="7" t="s">
@@ -2855,7 +2883,7 @@
       <c r="F3" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="22" t="s">
         <v>148</v>
       </c>
       <c r="H3" s="7" t="s">
@@ -2875,28 +2903,28 @@
       <c r="B4" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="G4" s="24" t="s">
         <v>155</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="18" t="s">
         <v>156</v>
       </c>
       <c r="I4" s="7">
         <v>5</v>
       </c>
-      <c r="J4" s="17" t="s">
+      <c r="J4" s="18" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2907,28 +2935,28 @@
       <c r="B5" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="25" t="s">
         <v>161</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="G5" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="18" t="s">
         <v>164</v>
       </c>
       <c r="I5" s="7">
         <v>4</v>
       </c>
-      <c r="J5" s="17" t="s">
+      <c r="J5" s="18" t="s">
         <v>165</v>
       </c>
     </row>
@@ -2939,7 +2967,7 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="19"/>
+      <c r="G6" s="20"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -3006,7 +3034,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="220.8" spans="1:10">
+    <row r="2" ht="110.4" spans="1:10">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -3038,8 +3066,10 @@
         <v>174</v>
       </c>
     </row>
-    <row r="3" ht="259.2" spans="1:10">
-      <c r="A3" s="9"/>
+    <row r="3" ht="115.2" spans="1:10">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
       <c r="B3" s="10" t="s">
         <v>54</v>
       </c>
@@ -3078,13 +3108,13 @@
       <c r="C4" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="14" t="s">
         <v>186</v>
       </c>
       <c r="G4" s="8" t="s">
@@ -3104,31 +3134,31 @@
       <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="15" t="s">
         <v>54</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="17" t="s">
         <v>192</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="18" t="s">
         <v>194</v>
       </c>
       <c r="I5" s="7">
         <v>5</v>
       </c>
-      <c r="J5" s="17" t="s">
+      <c r="J5" s="18" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3137,20 +3167,20 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="E6" s="7"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="20"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="F7" s="16"/>
+      <c r="F7" s="17"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="F8" s="18"/>
+      <c r="F8" s="19"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="F9" s="16"/>
+      <c r="F9" s="17"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3167,6 +3197,161 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="34.8888888888889" customWidth="1"/>
+    <col min="6" max="6" width="75" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="32.4444444444444" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="61.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:10">
+      <c r="A1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" ht="76" customHeight="1" spans="1:10">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="I2" s="7">
+        <v>5</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="3" ht="114" customHeight="1" spans="1:10">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="11"/>
+    </row>
+    <row r="4" ht="157.2" customHeight="1" spans="1:10">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+    </row>
+    <row r="5" ht="168" customHeight="1" spans="1:10">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="15"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="18"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="F7" s="17"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="F8" s="19"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="F9" s="17"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" display="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/2584cd05cdc1b59d1bc66b29b55425e534f5034d"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
@@ -3176,10 +3361,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -3187,7 +3372,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" ht="26.4" customHeight="1" spans="1:2">
@@ -3195,7 +3380,7 @@
         <v>37</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" ht="26.4" customHeight="1" spans="1:2">
@@ -3203,7 +3388,7 @@
         <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3211,7 +3396,7 @@
         <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" ht="26.4" customHeight="1" spans="1:2">
@@ -3219,7 +3404,7 @@
         <v>40</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" ht="26.4" customHeight="1" spans="1:2">
@@ -3227,7 +3412,7 @@
         <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" ht="39.6" customHeight="1" spans="1:2">
@@ -3235,7 +3420,7 @@
         <v>42</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" ht="26.4" customHeight="1" spans="1:2">
@@ -3243,7 +3428,7 @@
         <v>43</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3251,7 +3436,7 @@
         <v>44</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" ht="26.4" customHeight="1" spans="1:2">
@@ -3259,7 +3444,7 @@
         <v>45</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/docs/PRJ301_SE20C_GROUP4 .xlsx
+++ b/docs/PRJ301_SE20C_GROUP4 .xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tuong Vy\Documents\GitHub\PRJ---24-7-LLM-Tutor\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D528CE1-5D15-4CF0-99CC-F454EE293670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10440" activeTab="6"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -17,24 +23,11 @@
     <sheet name="Instruction" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="223">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -580,7 +573,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Generated the basic CRUD structure for </t>
@@ -599,7 +592,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> and </t>
@@ -618,7 +611,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
@@ -748,18 +741,33 @@
   <si>
     <t>What limitations or risks you observed when using AI (e.g., “generated SQL injection-prone code”, “missing validation logic”, “incomplete test coverage”).</t>
   </si>
+  <si>
+    <t>Implement class management for lecturers (ClassServlet, ClassDAO, classes.jsp).</t>
+  </si>
+  <si>
+    <t>Gemini, ChatGPT</t>
+  </si>
+  <si>
+    <t>Generated/refined the ClassServlet and ClassDAO structure and the classes.jsp page for displaying and managing classes.</t>
+  </si>
+  <si>
+    <t>Reviewed the generated code and adapted it to the Java Web project: connected ClassDAO to the existing DBContext, matched table and column names with the SQL Server database, checked input validation in the servlet, and tested the page on Tomcat.</t>
+  </si>
+  <si>
+    <t>1 Servlet (ClassServlet), 1 DAO (ClassDAO), 1 class view page (classes.jsp).</t>
+  </si>
+  <si>
+    <t>Generated code may not fit the existing database schema or naming, so manual fixes were needed. SQL queries and error handling had to be checked by hand. Access control (only lecturers can open the page) is not handled by the AI unless it is added and tested separately.</t>
+  </si>
+  <si>
+    <t>https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/3901ac5418d96497394a4d6afe77c7064be455f6</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-  </numFmts>
-  <fonts count="30">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -772,51 +780,51 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -824,149 +832,20 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -976,7 +855,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1007,194 +886,8 @@
         <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1254,249 +947,10 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1523,151 +977,108 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1952,20 +1363,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.05" customHeight="1" spans="1:5">
+    <row r="1" spans="1:5" ht="28.05" customHeight="1">
       <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
@@ -1975,10 +1386,10 @@
       <c r="E1" s="35"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="36" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="34"/>
@@ -1986,10 +1397,10 @@
       <c r="E3" s="35"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="36" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="34"/>
@@ -1997,10 +1408,10 @@
       <c r="E4" s="35"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="36" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="34"/>
@@ -2008,10 +1419,10 @@
       <c r="E5" s="35"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="36" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="34"/>
@@ -2019,10 +1430,10 @@
       <c r="E6" s="35"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="36" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="34"/>
@@ -2030,10 +1441,10 @@
       <c r="E7" s="35"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="37">
+      <c r="B8" s="36">
         <v>4</v>
       </c>
       <c r="C8" s="34"/>
@@ -2041,10 +1452,10 @@
       <c r="E8" s="35"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="36" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="34"/>
@@ -2052,7 +1463,7 @@
       <c r="E9" s="35"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="37" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="34"/>
@@ -2078,112 +1489,110 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="38">
+      <c r="A13" s="32">
         <v>1</v>
       </c>
-      <c r="B13" s="37" t="s">
+      <c r="B13" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="C13" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="37" t="s">
+      <c r="D13" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="37" t="s">
+      <c r="E13" s="31" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="38">
+      <c r="A14" s="32">
         <v>2</v>
       </c>
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="37" t="s">
+      <c r="E14" s="31" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" ht="26.4" customHeight="1" spans="1:5">
-      <c r="A15" s="38">
+    <row r="15" spans="1:5" ht="26.4" customHeight="1">
+      <c r="A15" s="32">
         <v>3</v>
       </c>
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="37" t="s">
+      <c r="D15" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="37" t="s">
+      <c r="E15" s="31" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="38">
+      <c r="A16" s="32">
         <v>4</v>
       </c>
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="37" t="s">
+      <c r="D16" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="37" t="s">
+      <c r="E16" s="31" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="38">
+      <c r="A17" s="32">
         <v>5</v>
       </c>
-      <c r="B17" s="37" t="s">
+      <c r="B17" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="C17" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="37" t="s">
+      <c r="D17" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="37" t="s">
+      <c r="E17" s="31" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="A11:E11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2197,7 +1606,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -2229,124 +1638,122 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="96" customHeight="1" spans="1:10">
+    <row r="2" spans="1:10" ht="96" customHeight="1">
       <c r="A2" s="13">
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="11" t="s">
         <v>47</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="G2" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="11">
         <v>5</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="11" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" ht="108" customHeight="1" spans="1:10">
+    <row r="3" spans="1:10" ht="108" customHeight="1">
       <c r="A3" s="13">
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="11" t="s">
         <v>55</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="11" t="s">
         <v>59</v>
       </c>
       <c r="I3" s="13">
         <v>4</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="4" ht="115.2" customHeight="1" spans="1:10">
+    <row r="4" spans="1:10" ht="115.2" customHeight="1">
       <c r="A4" s="13">
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="11" t="s">
         <v>62</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="11" t="s">
         <v>67</v>
       </c>
       <c r="I4" s="13">
         <v>4</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="11" t="s">
         <v>68</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link" tooltip="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link"/>
-    <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing" tooltip="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing"/>
-    <hyperlink ref="G4" r:id="rId3" display="https://drive.google.com/drive/folders/1hkfM8Mek8vMbZPqjB3AijcdotsKPLGua?usp=sharing"/>
+    <hyperlink ref="G2" r:id="rId1" tooltip="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="G3" r:id="rId2" tooltip="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="38.3333333333333" customWidth="1"/>
-    <col min="4" max="4" width="15.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="31.4351851851852" customWidth="1"/>
+    <col min="3" max="3" width="38.33203125" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="31.44140625" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
@@ -2354,7 +1761,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -2386,184 +1793,182 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="121.05" customHeight="1" spans="1:10">
+    <row r="2" spans="1:10" ht="121.05" customHeight="1">
       <c r="A2" s="13">
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="11">
         <v>5</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="11" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="3" ht="142.95" customHeight="1" spans="1:10">
+    <row r="3" spans="1:10" ht="142.94999999999999" customHeight="1">
       <c r="A3" s="13">
         <v>2</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="G3" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="11" t="s">
         <v>81</v>
       </c>
       <c r="I3" s="13">
         <v>5</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" ht="139.05" customHeight="1" spans="1:10">
+    <row r="4" spans="1:10" ht="139.05000000000001" customHeight="1">
       <c r="A4" s="13">
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="11" t="s">
         <v>83</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="11" t="s">
         <v>88</v>
       </c>
       <c r="I4" s="13">
         <v>4</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="11" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" ht="187.2" customHeight="1" spans="1:10">
+    <row r="5" spans="1:10" ht="187.2" customHeight="1">
       <c r="A5" s="13">
         <v>4</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="G5" s="30" t="s">
+      <c r="G5" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H5" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="11">
         <v>4</v>
       </c>
-      <c r="J5" s="23" t="s">
+      <c r="J5" s="20" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="6" ht="144" customHeight="1" spans="1:10">
+    <row r="6" spans="1:10" ht="144" customHeight="1">
       <c r="A6" s="13">
         <v>5</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H6" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="11">
         <v>5</v>
       </c>
-      <c r="J6" s="27" t="s">
+      <c r="J6" s="24" t="s">
         <v>101</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1MvIEKYq72RDwufT_sIZ_XiyqlYSTz0PZ?usp=sharing"/>
-    <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1TsNLKc7zhuCoEUPjxf-lhVzScFA5SqKi?usp=sharing"/>
-    <hyperlink ref="G4" r:id="rId3" display="https://drive.google.com/drive/folders/1jfv8FE53NmF0-9jNc803u7VXSKQBN8MB?usp=sharing"/>
-    <hyperlink ref="G5" r:id="rId4" display="https://drive.google.com/drive/folders/1_IiKnUxj3SQwrN2uhQHVUB0enmRgof_9?usp=sharing"/>
-    <hyperlink ref="G6" r:id="rId5" display="https://drive.google.com/drive/folders/1Cv8UVkfH270j3_3KHpU-v4wu6AA63oxH?hl=vi"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2577,7 +1982,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -2609,7 +2014,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="86.4" customHeight="1" spans="1:10">
+    <row r="2" spans="1:10" ht="86.4" customHeight="1">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -2628,7 +2033,7 @@
       <c r="F2" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="18" t="s">
         <v>106</v>
       </c>
       <c r="H2" s="7" t="s">
@@ -2641,7 +2046,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" ht="72" customHeight="1" spans="1:10">
+    <row r="3" spans="1:10" ht="72" customHeight="1">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -2660,7 +2065,7 @@
       <c r="F3" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="18" t="s">
         <v>113</v>
       </c>
       <c r="H3" s="7" t="s">
@@ -2673,7 +2078,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4" ht="72" customHeight="1" spans="1:10">
+    <row r="4" spans="1:10" ht="72" customHeight="1">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -2692,7 +2097,7 @@
       <c r="F4" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="18" t="s">
         <v>120</v>
       </c>
       <c r="H4" s="7" t="s">
@@ -2705,7 +2110,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" ht="86.4" customHeight="1" spans="1:10">
+    <row r="5" spans="1:10" ht="86.4" customHeight="1">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -2724,7 +2129,7 @@
       <c r="F5" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="18" t="s">
         <v>126</v>
       </c>
       <c r="H5" s="7" t="s">
@@ -2737,7 +2142,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="6" ht="82.8" customHeight="1" spans="1:10">
+    <row r="6" spans="1:10" ht="82.8" customHeight="1">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -2756,7 +2161,7 @@
       <c r="F6" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="18" t="s">
         <v>133</v>
       </c>
       <c r="H6" s="7" t="s">
@@ -2771,22 +2176,20 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1Al2zQH-_4wk5DT_6O8csILsFFIXu45rO?usp=sharing"/>
-    <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1mkeoPv7QBeEjPVionr3T6jgvSR-VMuW3?usp=sharing"/>
-    <hyperlink ref="G4" r:id="rId3" display="https://drive.google.com/drive/folders/1BT8UQCi9wl8cJyHOPO71V5_QBshXmKtW?usp=sharing"/>
-    <hyperlink ref="G5" r:id="rId4" display="https://drive.google.com/drive/folders/1HDAnlKy5GQiDcsJ5ka-zU_YZRkGuqeTY?usp=sharing"/>
-    <hyperlink ref="G6" r:id="rId5" display="https://drive.google.com/drive/folders/18528q5unPQgaTq-89bPzC0Es6qiiTV2f?usp=sharing"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{00000000-0004-0000-0300-000003000000}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{00000000-0004-0000-0300-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2800,7 +2203,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -2832,7 +2235,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="110.4" customHeight="1" spans="1:10">
+    <row r="2" spans="1:10" ht="110.4" customHeight="1">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -2851,7 +2254,7 @@
       <c r="F2" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="18" t="s">
         <v>141</v>
       </c>
       <c r="H2" s="7" t="s">
@@ -2864,7 +2267,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="3" ht="169.95" customHeight="1" spans="1:10">
+    <row r="3" spans="1:10" ht="169.95" customHeight="1">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -2883,7 +2286,7 @@
       <c r="F3" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="19" t="s">
         <v>148</v>
       </c>
       <c r="H3" s="7" t="s">
@@ -2896,67 +2299,67 @@
         <v>150</v>
       </c>
     </row>
-    <row r="4" ht="82.8" spans="1:10">
+    <row r="4" spans="1:10" ht="82.8">
       <c r="A4" s="9">
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="16" t="s">
         <v>156</v>
       </c>
       <c r="I4" s="7">
         <v>5</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="16" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="5" ht="82.8" spans="1:10">
+    <row r="5" spans="1:10" ht="82.8">
       <c r="A5" s="9">
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="G5" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="16" t="s">
         <v>164</v>
       </c>
       <c r="I5" s="7">
         <v>4</v>
       </c>
-      <c r="J5" s="18" t="s">
+      <c r="J5" s="16" t="s">
         <v>165</v>
       </c>
     </row>
@@ -2967,26 +2370,24 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="20"/>
+      <c r="G6" s="17"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1uyrqO7T6EU5SHkkqS9n9vUqZ1ghX6fXp?usp=sharing"/>
-    <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1C72WWLyzh_2zq-OIQMlprdEkDgRMdWwf?usp=sharing"/>
-    <hyperlink ref="G4" r:id="rId3" display="https://drive.google.com/drive/folders/1-OKCkuc_DCyRqRFaBMpfMPzjAfGv7iIW?usp=sharing"/>
-    <hyperlink ref="G5" r:id="rId4" display="https://drive.google.com/drive/folders/1iBfU8OXqMzE1mJFvxObm1NvyRtSjh1Ub?usp=sharing" tooltip="https://drive.google.com/drive/folders/1iBfU8OXqMzE1mJFvxObm1NvyRtSjh1Ub?usp=sharing"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
+    <hyperlink ref="G5" r:id="rId4" tooltip="https://drive.google.com/drive/folders/1iBfU8OXqMzE1mJFvxObm1NvyRtSjh1Ub?usp=sharing" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
@@ -2994,15 +2395,15 @@
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="34.8888888888889" customWidth="1"/>
+    <col min="5" max="5" width="34.88671875" customWidth="1"/>
     <col min="6" max="6" width="75" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="32.4444444444444" customWidth="1"/>
+    <col min="8" max="8" width="32.44140625" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="61.7777777777778" customWidth="1"/>
+    <col min="10" max="10" width="61.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -3034,7 +2435,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="110.4" spans="1:10">
+    <row r="2" spans="1:10" ht="110.4">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -3066,7 +2467,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="3" ht="115.2" spans="1:10">
+    <row r="3" spans="1:10" ht="115.2">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -3098,7 +2499,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="4" ht="157.2" customHeight="1" spans="1:10">
+    <row r="4" spans="1:10" ht="157.19999999999999" customHeight="1">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -3111,10 +2512,10 @@
       <c r="D4" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="11" t="s">
         <v>186</v>
       </c>
       <c r="G4" s="8" t="s">
@@ -3130,35 +2531,35 @@
         <v>189</v>
       </c>
     </row>
-    <row r="5" ht="168" customHeight="1" spans="1:10">
+    <row r="5" spans="1:10" ht="168" customHeight="1">
       <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="10" t="s">
         <v>54</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="15" t="s">
         <v>192</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="16" t="s">
         <v>194</v>
       </c>
       <c r="I5" s="7">
         <v>5</v>
       </c>
-      <c r="J5" s="18" t="s">
+      <c r="J5" s="16" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3167,36 +2568,34 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="E6" s="7"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="20"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="17"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="F7" s="17"/>
+      <c r="F7" s="15"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="F8" s="19"/>
+      <c r="F8" s="15"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="F9" s="17"/>
+      <c r="F9" s="15"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/cf570a4" tooltip="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/cf570a4"/>
-    <hyperlink ref="G5" r:id="rId2" display="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/fb3e135"/>
-    <hyperlink ref="G4" r:id="rId3" display="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/12eb884"/>
-    <hyperlink ref="G3" r:id="rId4" display="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/3901ac5"/>
+    <hyperlink ref="G2" r:id="rId1" tooltip="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/cf570a4" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
+    <hyperlink ref="G5" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
+    <hyperlink ref="G3" r:id="rId4" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:J9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
@@ -3204,15 +2603,15 @@
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="34.8888888888889" customWidth="1"/>
+    <col min="5" max="5" width="34.88671875" customWidth="1"/>
     <col min="6" max="6" width="75" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="32.4444444444444" customWidth="1"/>
+    <col min="8" max="8" width="32.44140625" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="61.7777777777778" customWidth="1"/>
+    <col min="10" max="10" width="61.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -3244,7 +2643,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="76" customHeight="1" spans="1:10">
+    <row r="2" spans="1:10" ht="76.05" customHeight="1">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -3276,47 +2675,65 @@
         <v>203</v>
       </c>
     </row>
-    <row r="3" ht="114" customHeight="1" spans="1:10">
+    <row r="3" spans="1:10" ht="114" customHeight="1">
       <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="11"/>
-    </row>
-    <row r="4" ht="157.2" customHeight="1" spans="1:10">
+      <c r="B3" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="C3" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E3" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="F3" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="H3" s="38" t="s">
+        <v>220</v>
+      </c>
+      <c r="I3" s="7">
+        <v>4</v>
+      </c>
+      <c r="J3" s="38" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="157.19999999999999" customHeight="1">
       <c r="A4" s="9">
         <v>3</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="13"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" ht="168" customHeight="1" spans="1:10">
+    <row r="5" spans="1:10" ht="168" customHeight="1">
       <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="15"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="17"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="15"/>
       <c r="G5" s="8"/>
-      <c r="H5" s="18"/>
+      <c r="H5" s="16"/>
       <c r="I5" s="7"/>
-      <c r="J5" s="18"/>
+      <c r="J5" s="16"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="9">
@@ -3325,35 +2742,33 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="E6" s="7"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="20"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="17"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="F7" s="17"/>
+      <c r="F7" s="15"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="F8" s="19"/>
+      <c r="F8" s="15"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="F9" s="17"/>
+      <c r="F9" s="15"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/2584cd05cdc1b59d1bc66b29b55425e534f5034d"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
@@ -3375,7 +2790,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="3" ht="26.4" customHeight="1" spans="1:2">
+    <row r="3" spans="1:2" ht="26.4" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>37</v>
       </c>
@@ -3383,7 +2798,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="4" ht="26.4" customHeight="1" spans="1:2">
+    <row r="4" spans="1:2" ht="26.4" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>38</v>
       </c>
@@ -3399,7 +2814,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="6" ht="26.4" customHeight="1" spans="1:2">
+    <row r="6" spans="1:2" ht="26.4" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>40</v>
       </c>
@@ -3407,7 +2822,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="7" ht="26.4" customHeight="1" spans="1:2">
+    <row r="7" spans="1:2" ht="26.4" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
@@ -3415,7 +2830,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="8" ht="39.6" customHeight="1" spans="1:2">
+    <row r="8" spans="1:2" ht="39.6" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>42</v>
       </c>
@@ -3423,7 +2838,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="9" ht="26.4" customHeight="1" spans="1:2">
+    <row r="9" spans="1:2" ht="26.4" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>43</v>
       </c>
@@ -3439,7 +2854,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="11" ht="26.4" customHeight="1" spans="1:2">
+    <row r="11" spans="1:2" ht="26.4" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>45</v>
       </c>
@@ -3449,6 +2864,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/docs/PRJ301_SE20C_GROUP4 .xlsx
+++ b/docs/PRJ301_SE20C_GROUP4 .xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10440" activeTab="6"/>
+    <workbookView windowWidth="23040" windowHeight="9000" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="221">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -711,6 +711,21 @@
     <t>AI response quality depends on the selected model and prompt. External API calls can fail because of missing API keys, network timeouts, quota limits, or provider outages. Live API behavior must be tested with valid credentials.</t>
   </si>
   <si>
+    <t>Implement personalized learning path from chat content: AI topic recognition, path generation, student completion-status updates, and lecturer/admin summary view</t>
+  </si>
+  <si>
+    <t>LearningPathServlet logic that detects the knowledge topic from a technical question and builds an ordered path; LearningPathDAO (insert, load by student, update status); LearningPath model; learning-path.jsp with path, status controls and a lecturer/admin summary</t>
+  </si>
+  <si>
+    <t>Adapted the code to the MVC structure and the Personalized_Learning_Paths table, limited topics to the PRJ301 syllabus, validated empty input, used parameterized queries and EL/&lt;c:out&gt;, added ownership and role checks, and tested the flow chat → path → status update → summary</t>
+  </si>
+  <si>
+    <t>1 Servlet (LearningPathServlet); 1 DAO (LearningPathDAO); 1 model (LearningPath); 1 JSP (learning-path.jsp)</t>
+  </si>
+  <si>
+    <t>AI may misclassify vague or off-topic questions and suggest topics outside the PRJ301 scope; generated SQL had to be matched to the real schema; ownership and role checks were missing and were added manually</t>
+  </si>
+  <si>
     <t>Column</t>
   </si>
   <si>
@@ -754,10 +769,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="30">
     <font>
@@ -800,7 +815,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -814,7 +829,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1358,19 +1373,19 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1500,7 +1515,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1523,20 +1538,20 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1544,6 +1559,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1559,43 +1577,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1966,99 +1987,99 @@
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:5">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="37"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="35"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="37"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="35"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="37"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="35"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="37"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="35"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="37"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="35"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="37"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="37">
+      <c r="B8" s="39">
         <v>4</v>
       </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="35"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="37"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="35"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="37"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="35"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="37"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
@@ -2078,87 +2099,87 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="38">
+      <c r="A13" s="40">
         <v>1</v>
       </c>
-      <c r="B13" s="37" t="s">
+      <c r="B13" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="C13" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="37" t="s">
+      <c r="D13" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="37" t="s">
+      <c r="E13" s="39" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="38">
+      <c r="A14" s="40">
         <v>2</v>
       </c>
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="37" t="s">
+      <c r="E14" s="39" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" ht="26.4" customHeight="1" spans="1:5">
-      <c r="A15" s="38">
+      <c r="A15" s="40">
         <v>3</v>
       </c>
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="37" t="s">
+      <c r="D15" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="37" t="s">
+      <c r="E15" s="39" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="38">
+      <c r="A16" s="40">
         <v>4</v>
       </c>
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="37" t="s">
+      <c r="D16" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="37" t="s">
+      <c r="E16" s="39" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="38">
+      <c r="A17" s="40">
         <v>5</v>
       </c>
-      <c r="B17" s="37" t="s">
+      <c r="B17" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="C17" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="37" t="s">
+      <c r="D17" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="37" t="s">
+      <c r="E17" s="39" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2248,7 +2269,7 @@
       <c r="F2" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="G2" s="34" t="s">
         <v>51</v>
       </c>
       <c r="H2" s="14" t="s">
@@ -2280,7 +2301,7 @@
       <c r="F3" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="34" t="s">
         <v>58</v>
       </c>
       <c r="H3" s="14" t="s">
@@ -2312,7 +2333,7 @@
       <c r="F4" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="30" t="s">
         <v>66</v>
       </c>
       <c r="H4" s="14" t="s">
@@ -2399,13 +2420,13 @@
       <c r="D2" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="29" t="s">
         <v>70</v>
       </c>
       <c r="F2" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="30" t="s">
         <v>72</v>
       </c>
       <c r="H2" s="14" t="s">
@@ -2437,7 +2458,7 @@
       <c r="F3" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="G3" s="30" t="s">
         <v>80</v>
       </c>
       <c r="H3" s="14" t="s">
@@ -2469,7 +2490,7 @@
       <c r="F4" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="30" t="s">
         <v>87</v>
       </c>
       <c r="H4" s="14" t="s">
@@ -2486,31 +2507,31 @@
       <c r="A5" s="13">
         <v>4</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="G5" s="30" t="s">
+      <c r="G5" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H5" s="25" t="s">
         <v>94</v>
       </c>
       <c r="I5" s="14">
         <v>4</v>
       </c>
-      <c r="J5" s="23" t="s">
+      <c r="J5" s="25" t="s">
         <v>95</v>
       </c>
     </row>
@@ -2518,31 +2539,31 @@
       <c r="A6" s="13">
         <v>5</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="16" t="s">
         <v>84</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H6" s="29" t="s">
         <v>100</v>
       </c>
       <c r="I6" s="14">
         <v>5</v>
       </c>
-      <c r="J6" s="27" t="s">
+      <c r="J6" s="29" t="s">
         <v>101</v>
       </c>
     </row>
@@ -2628,7 +2649,7 @@
       <c r="F2" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="23" t="s">
         <v>106</v>
       </c>
       <c r="H2" s="7" t="s">
@@ -2660,7 +2681,7 @@
       <c r="F3" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="23" t="s">
         <v>113</v>
       </c>
       <c r="H3" s="7" t="s">
@@ -2692,7 +2713,7 @@
       <c r="F4" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="23" t="s">
         <v>120</v>
       </c>
       <c r="H4" s="7" t="s">
@@ -2724,7 +2745,7 @@
       <c r="F5" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="23" t="s">
         <v>126</v>
       </c>
       <c r="H5" s="7" t="s">
@@ -2756,7 +2777,7 @@
       <c r="F6" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="23" t="s">
         <v>133</v>
       </c>
       <c r="H6" s="7" t="s">
@@ -2851,7 +2872,7 @@
       <c r="F2" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="23" t="s">
         <v>141</v>
       </c>
       <c r="H2" s="7" t="s">
@@ -2883,7 +2904,7 @@
       <c r="F3" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="24" t="s">
         <v>148</v>
       </c>
       <c r="H3" s="7" t="s">
@@ -2903,28 +2924,28 @@
       <c r="B4" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="19" t="s">
         <v>156</v>
       </c>
       <c r="I4" s="7">
         <v>5</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="19" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2935,28 +2956,28 @@
       <c r="B5" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="G5" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="19" t="s">
         <v>164</v>
       </c>
       <c r="I5" s="7">
         <v>4</v>
       </c>
-      <c r="J5" s="18" t="s">
+      <c r="J5" s="19" t="s">
         <v>165</v>
       </c>
     </row>
@@ -2967,7 +2988,7 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="20"/>
+      <c r="G6" s="21"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -3053,7 +3074,7 @@
       <c r="F2" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="15" t="s">
         <v>171</v>
       </c>
       <c r="H2" s="7" t="s">
@@ -3070,7 +3091,7 @@
       <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="22" t="s">
         <v>54</v>
       </c>
       <c r="C3" s="11" t="s">
@@ -3085,7 +3106,7 @@
       <c r="F3" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="15" t="s">
         <v>179</v>
       </c>
       <c r="H3" s="7" t="s">
@@ -3117,7 +3138,7 @@
       <c r="F4" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="15" t="s">
         <v>187</v>
       </c>
       <c r="H4" s="7" t="s">
@@ -3134,7 +3155,7 @@
       <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>54</v>
       </c>
       <c r="C5" s="7" t="s">
@@ -3143,22 +3164,22 @@
       <c r="D5" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="19" t="s">
         <v>194</v>
       </c>
       <c r="I5" s="7">
         <v>5</v>
       </c>
-      <c r="J5" s="18" t="s">
+      <c r="J5" s="19" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3167,20 +3188,20 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="E6" s="7"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="F7" s="17"/>
+      <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="F8" s="19"/>
+      <c r="F8" s="20"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="F9" s="17"/>
+      <c r="F9" s="18"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3280,15 +3301,33 @@
       <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="11"/>
+      <c r="B3" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="I3" s="7">
+        <v>4</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="4" ht="157.2" customHeight="1" spans="1:10">
       <c r="A4" s="9">
@@ -3299,7 +3338,7 @@
       <c r="D4" s="13"/>
       <c r="E4" s="14"/>
       <c r="F4" s="14"/>
-      <c r="G4" s="8"/>
+      <c r="G4" s="15"/>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
@@ -3308,15 +3347,15 @@
       <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="15"/>
+      <c r="B5" s="16"/>
       <c r="C5" s="7"/>
       <c r="D5" s="14"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="18"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="19"/>
       <c r="I5" s="7"/>
-      <c r="J5" s="18"/>
+      <c r="J5" s="19"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="9">
@@ -3325,24 +3364,24 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="E6" s="7"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="F7" s="17"/>
+      <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="F8" s="19"/>
+      <c r="F8" s="20"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="F9" s="17"/>
+      <c r="F9" s="18"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/2584cd05cdc1b59d1bc66b29b55425e534f5034d"/>
+    <hyperlink ref="G2" r:id="rId1" display="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/2584cd05cdc1b59d1bc66b29b55425e534f5034d" tooltip="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/2584cd05cdc1b59d1bc66b29b55425e534f5034d"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -3361,10 +3400,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -3372,7 +3411,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" ht="26.4" customHeight="1" spans="1:2">
@@ -3380,7 +3419,7 @@
         <v>37</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" ht="26.4" customHeight="1" spans="1:2">
@@ -3388,7 +3427,7 @@
         <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3396,7 +3435,7 @@
         <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" ht="26.4" customHeight="1" spans="1:2">
@@ -3404,7 +3443,7 @@
         <v>40</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" ht="26.4" customHeight="1" spans="1:2">
@@ -3412,7 +3451,7 @@
         <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" ht="39.6" customHeight="1" spans="1:2">
@@ -3420,7 +3459,7 @@
         <v>42</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" ht="26.4" customHeight="1" spans="1:2">
@@ -3428,7 +3467,7 @@
         <v>43</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3436,7 +3475,7 @@
         <v>44</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" ht="26.4" customHeight="1" spans="1:2">
@@ -3444,7 +3483,7 @@
         <v>45</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>

--- a/docs/PRJ301_SE20C_GROUP4 .xlsx
+++ b/docs/PRJ301_SE20C_GROUP4 .xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tuong Vy\Documents\GitHub\PRJ---24-7-LLM-Tutor\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9618B291-CC9D-4A77-9D83-13864DCC7367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" activeTab="6"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -17,24 +23,11 @@
     <sheet name="Instruction" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="227">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -580,7 +573,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Generated the basic CRUD structure for </t>
@@ -599,7 +592,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> and </t>
@@ -618,7 +611,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
@@ -763,18 +756,30 @@
   <si>
     <t>What limitations or risks you observed when using AI (e.g., “generated SQL injection-prone code”, “missing validation logic”, “incomplete test coverage”).</t>
   </si>
+  <si>
+    <t>Implement class management for lecturers (ClassServlet, ClassDAO, classes.jsp).</t>
+  </si>
+  <si>
+    <t>Generated/refined the ClassServlet and ClassDAO structure and the classes.jsp page for displaying and managing classes.</t>
+  </si>
+  <si>
+    <t>Reviewed the generated code and adapted it to the Java Web project: connected ClassDAO to the existing DBContext, matched table and column names with the SQL Server database, checked input validation in the servlet, and tested the page on Tomcat.</t>
+  </si>
+  <si>
+    <t>1 Servlet (ClassServlet), 1 DAO (ClassDAO), 1 class view page (classes.jsp).</t>
+  </si>
+  <si>
+    <t>Generated code may not fit the existing database schema or naming, so manual fixes were needed. SQL queries and error handling had to be checked by hand. Access control (only lecturers can open the page) is not handled by the AI unless it is added and tested separately.</t>
+  </si>
+  <si>
+    <t>https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/3901ac5418d96497394a4d6afe77c7064be455f6</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="30">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -787,51 +792,51 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -839,149 +844,20 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -991,7 +867,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1022,194 +898,8 @@
         <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1269,253 +959,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1538,28 +989,25 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1568,127 +1016,81 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1973,113 +1375,113 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.05" customHeight="1" spans="1:5">
-      <c r="A1" s="35" t="s">
+    <row r="1" spans="1:5" ht="28.05" customHeight="1">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="37"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="35"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="37"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="35"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="37"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="35"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="37"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="35"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="37"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="35"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="37"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="35"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="39">
+      <c r="B8" s="36">
         <v>4</v>
       </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="37"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="35"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="37"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="35"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="37"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="35"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
@@ -2099,112 +1501,110 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="40">
+      <c r="A13" s="32">
         <v>1</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="39" t="s">
+      <c r="D13" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="39" t="s">
+      <c r="E13" s="31" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="40">
+      <c r="A14" s="32">
         <v>2</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="39" t="s">
+      <c r="E14" s="31" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" ht="26.4" customHeight="1" spans="1:5">
-      <c r="A15" s="40">
+    <row r="15" spans="1:5" ht="26.4" customHeight="1">
+      <c r="A15" s="32">
         <v>3</v>
       </c>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="39" t="s">
+      <c r="E15" s="31" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="40">
+      <c r="A16" s="32">
         <v>4</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="39" t="s">
+      <c r="E16" s="31" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="40">
+      <c r="A17" s="32">
         <v>5</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="39" t="s">
+      <c r="D17" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="39" t="s">
+      <c r="E17" s="31" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="A11:E11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2218,7 +1618,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -2250,124 +1650,122 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="96" customHeight="1" spans="1:10">
+    <row r="2" spans="1:10" ht="96" customHeight="1">
       <c r="A2" s="13">
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="11" t="s">
         <v>47</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="G2" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="11">
         <v>5</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="11" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" ht="108" customHeight="1" spans="1:10">
+    <row r="3" spans="1:10" ht="108" customHeight="1">
       <c r="A3" s="13">
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="11" t="s">
         <v>55</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="34" t="s">
+      <c r="G3" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="11" t="s">
         <v>59</v>
       </c>
       <c r="I3" s="13">
         <v>4</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="4" ht="115.2" customHeight="1" spans="1:10">
+    <row r="4" spans="1:10" ht="115.2" customHeight="1">
       <c r="A4" s="13">
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="11" t="s">
         <v>62</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="G4" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="11" t="s">
         <v>67</v>
       </c>
       <c r="I4" s="13">
         <v>4</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="11" t="s">
         <v>68</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link" tooltip="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link"/>
-    <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing" tooltip="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing"/>
-    <hyperlink ref="G4" r:id="rId3" display="https://drive.google.com/drive/folders/1hkfM8Mek8vMbZPqjB3AijcdotsKPLGua?usp=sharing"/>
+    <hyperlink ref="G2" r:id="rId1" tooltip="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="G3" r:id="rId2" tooltip="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="38.3333333333333" customWidth="1"/>
-    <col min="4" max="4" width="15.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="31.4351851851852" customWidth="1"/>
+    <col min="3" max="3" width="38.33203125" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="31.44140625" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
@@ -2375,7 +1773,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -2407,184 +1805,182 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="121.05" customHeight="1" spans="1:10">
+    <row r="2" spans="1:10" ht="121.05" customHeight="1">
       <c r="A2" s="13">
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="11">
         <v>5</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="11" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="3" ht="142.95" customHeight="1" spans="1:10">
+    <row r="3" spans="1:10" ht="142.94999999999999" customHeight="1">
       <c r="A3" s="13">
         <v>2</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="G3" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="11" t="s">
         <v>81</v>
       </c>
       <c r="I3" s="13">
         <v>5</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" ht="139.05" customHeight="1" spans="1:10">
+    <row r="4" spans="1:10" ht="139.05000000000001" customHeight="1">
       <c r="A4" s="13">
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="11" t="s">
         <v>83</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="G4" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="11" t="s">
         <v>88</v>
       </c>
       <c r="I4" s="13">
         <v>4</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="11" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" ht="187.2" customHeight="1" spans="1:10">
+    <row r="5" spans="1:10" ht="187.2" customHeight="1">
       <c r="A5" s="13">
         <v>4</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="G5" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="H5" s="25" t="s">
+      <c r="H5" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="11">
         <v>4</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="22" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="6" ht="144" customHeight="1" spans="1:10">
+    <row r="6" spans="1:10" ht="144" customHeight="1">
       <c r="A6" s="13">
         <v>5</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F6" s="33" t="s">
+      <c r="F6" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="G6" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="H6" s="29" t="s">
+      <c r="H6" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="11">
         <v>5</v>
       </c>
-      <c r="J6" s="29" t="s">
+      <c r="J6" s="10" t="s">
         <v>101</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1MvIEKYq72RDwufT_sIZ_XiyqlYSTz0PZ?usp=sharing"/>
-    <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1TsNLKc7zhuCoEUPjxf-lhVzScFA5SqKi?usp=sharing"/>
-    <hyperlink ref="G4" r:id="rId3" display="https://drive.google.com/drive/folders/1jfv8FE53NmF0-9jNc803u7VXSKQBN8MB?usp=sharing"/>
-    <hyperlink ref="G5" r:id="rId4" display="https://drive.google.com/drive/folders/1_IiKnUxj3SQwrN2uhQHVUB0enmRgof_9?usp=sharing"/>
-    <hyperlink ref="G6" r:id="rId5" display="https://drive.google.com/drive/folders/1Cv8UVkfH270j3_3KHpU-v4wu6AA63oxH?hl=vi"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2598,7 +1994,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -2630,7 +2026,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="86.4" customHeight="1" spans="1:10">
+    <row r="2" spans="1:10" ht="86.4" customHeight="1">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -2649,7 +2045,7 @@
       <c r="F2" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="20" t="s">
         <v>106</v>
       </c>
       <c r="H2" s="7" t="s">
@@ -2662,7 +2058,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" ht="72" customHeight="1" spans="1:10">
+    <row r="3" spans="1:10" ht="72" customHeight="1">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -2681,7 +2077,7 @@
       <c r="F3" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="20" t="s">
         <v>113</v>
       </c>
       <c r="H3" s="7" t="s">
@@ -2694,7 +2090,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4" ht="72" customHeight="1" spans="1:10">
+    <row r="4" spans="1:10" ht="72" customHeight="1">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -2713,7 +2109,7 @@
       <c r="F4" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="G4" s="20" t="s">
         <v>120</v>
       </c>
       <c r="H4" s="7" t="s">
@@ -2726,7 +2122,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" ht="86.4" customHeight="1" spans="1:10">
+    <row r="5" spans="1:10" ht="86.4" customHeight="1">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -2745,7 +2141,7 @@
       <c r="F5" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="G5" s="20" t="s">
         <v>126</v>
       </c>
       <c r="H5" s="7" t="s">
@@ -2758,7 +2154,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="6" ht="82.8" customHeight="1" spans="1:10">
+    <row r="6" spans="1:10" ht="82.8" customHeight="1">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -2777,7 +2173,7 @@
       <c r="F6" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="20" t="s">
         <v>133</v>
       </c>
       <c r="H6" s="7" t="s">
@@ -2792,22 +2188,20 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1Al2zQH-_4wk5DT_6O8csILsFFIXu45rO?usp=sharing"/>
-    <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1mkeoPv7QBeEjPVionr3T6jgvSR-VMuW3?usp=sharing"/>
-    <hyperlink ref="G4" r:id="rId3" display="https://drive.google.com/drive/folders/1BT8UQCi9wl8cJyHOPO71V5_QBshXmKtW?usp=sharing"/>
-    <hyperlink ref="G5" r:id="rId4" display="https://drive.google.com/drive/folders/1HDAnlKy5GQiDcsJ5ka-zU_YZRkGuqeTY?usp=sharing"/>
-    <hyperlink ref="G6" r:id="rId5" display="https://drive.google.com/drive/folders/18528q5unPQgaTq-89bPzC0Es6qiiTV2f?usp=sharing"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{00000000-0004-0000-0300-000003000000}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{00000000-0004-0000-0300-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2821,7 +2215,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -2853,7 +2247,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="110.4" customHeight="1" spans="1:10">
+    <row r="2" spans="1:10" ht="110.4" customHeight="1">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -2872,7 +2266,7 @@
       <c r="F2" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="20" t="s">
         <v>141</v>
       </c>
       <c r="H2" s="7" t="s">
@@ -2885,7 +2279,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="3" ht="169.95" customHeight="1" spans="1:10">
+    <row r="3" spans="1:10" ht="169.95" customHeight="1">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -2904,7 +2298,7 @@
       <c r="F3" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="21" t="s">
         <v>148</v>
       </c>
       <c r="H3" s="7" t="s">
@@ -2917,67 +2311,67 @@
         <v>150</v>
       </c>
     </row>
-    <row r="4" ht="82.8" spans="1:10">
+    <row r="4" spans="1:10" ht="82.8">
       <c r="A4" s="9">
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="18" t="s">
         <v>156</v>
       </c>
       <c r="I4" s="7">
         <v>5</v>
       </c>
-      <c r="J4" s="19" t="s">
+      <c r="J4" s="18" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="5" ht="82.8" spans="1:10">
+    <row r="5" spans="1:10" ht="82.8">
       <c r="A5" s="9">
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="G5" s="28" t="s">
+      <c r="G5" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="18" t="s">
         <v>164</v>
       </c>
       <c r="I5" s="7">
         <v>4</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="18" t="s">
         <v>165</v>
       </c>
     </row>
@@ -2988,26 +2382,24 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="21"/>
+      <c r="G6" s="19"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1uyrqO7T6EU5SHkkqS9n9vUqZ1ghX6fXp?usp=sharing"/>
-    <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1C72WWLyzh_2zq-OIQMlprdEkDgRMdWwf?usp=sharing"/>
-    <hyperlink ref="G4" r:id="rId3" display="https://drive.google.com/drive/folders/1-OKCkuc_DCyRqRFaBMpfMPzjAfGv7iIW?usp=sharing"/>
-    <hyperlink ref="G5" r:id="rId4" display="https://drive.google.com/drive/folders/1iBfU8OXqMzE1mJFvxObm1NvyRtSjh1Ub?usp=sharing" tooltip="https://drive.google.com/drive/folders/1iBfU8OXqMzE1mJFvxObm1NvyRtSjh1Ub?usp=sharing"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
+    <hyperlink ref="G5" r:id="rId4" tooltip="https://drive.google.com/drive/folders/1iBfU8OXqMzE1mJFvxObm1NvyRtSjh1Ub?usp=sharing" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
@@ -3015,15 +2407,15 @@
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="34.8888888888889" customWidth="1"/>
+    <col min="5" max="5" width="34.88671875" customWidth="1"/>
     <col min="6" max="6" width="75" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="32.4444444444444" customWidth="1"/>
+    <col min="8" max="8" width="32.44140625" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="61.7777777777778" customWidth="1"/>
+    <col min="10" max="10" width="61.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -3055,7 +2447,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="110.4" spans="1:10">
+    <row r="2" spans="1:10" ht="110.4">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -3074,7 +2466,7 @@
       <c r="F2" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="14" t="s">
         <v>171</v>
       </c>
       <c r="H2" s="7" t="s">
@@ -3087,11 +2479,11 @@
         <v>174</v>
       </c>
     </row>
-    <row r="3" ht="115.2" spans="1:10">
+    <row r="3" spans="1:10" ht="115.2">
       <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="15" t="s">
         <v>54</v>
       </c>
       <c r="C3" s="11" t="s">
@@ -3106,7 +2498,7 @@
       <c r="F3" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="14" t="s">
         <v>179</v>
       </c>
       <c r="H3" s="7" t="s">
@@ -3119,7 +2511,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="4" ht="157.2" customHeight="1" spans="1:10">
+    <row r="4" spans="1:10" ht="157.19999999999999" customHeight="1">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -3132,13 +2524,13 @@
       <c r="D4" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="14" t="s">
         <v>187</v>
       </c>
       <c r="H4" s="7" t="s">
@@ -3151,35 +2543,35 @@
         <v>189</v>
       </c>
     </row>
-    <row r="5" ht="168" customHeight="1" spans="1:10">
+    <row r="5" spans="1:10" ht="168" customHeight="1">
       <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>54</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="18" t="s">
         <v>194</v>
       </c>
       <c r="I5" s="7">
         <v>5</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="18" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3188,36 +2580,34 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="E6" s="7"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="21"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="19"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="F7" s="18"/>
+      <c r="F7" s="17"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="F8" s="20"/>
+      <c r="F8" s="17"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="F9" s="18"/>
+      <c r="F9" s="17"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/cf570a4" tooltip="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/cf570a4"/>
-    <hyperlink ref="G5" r:id="rId2" display="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/fb3e135"/>
-    <hyperlink ref="G4" r:id="rId3" display="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/12eb884"/>
-    <hyperlink ref="G3" r:id="rId4" display="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/3901ac5"/>
+    <hyperlink ref="G2" r:id="rId1" tooltip="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/cf570a4" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
+    <hyperlink ref="G5" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
+    <hyperlink ref="G3" r:id="rId4" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:J9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
@@ -3225,15 +2615,15 @@
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="34.8888888888889" customWidth="1"/>
+    <col min="5" max="5" width="34.88671875" customWidth="1"/>
     <col min="6" max="6" width="75" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="32.4444444444444" customWidth="1"/>
+    <col min="8" max="8" width="32.44140625" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="61.7777777777778" customWidth="1"/>
+    <col min="10" max="10" width="61.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -3265,7 +2655,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="76" customHeight="1" spans="1:10">
+    <row r="2" spans="1:10" ht="76.05" customHeight="1">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -3297,7 +2687,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="3" ht="114" customHeight="1" spans="1:10">
+    <row r="3" spans="1:10" ht="114" customHeight="1">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -3329,33 +2719,51 @@
         <v>208</v>
       </c>
     </row>
-    <row r="4" ht="157.2" customHeight="1" spans="1:10">
+    <row r="4" spans="1:10" ht="157.19999999999999" customHeight="1">
       <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-    </row>
-    <row r="5" ht="168" customHeight="1" spans="1:10">
+      <c r="B4" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="E4" s="38" t="s">
+        <v>222</v>
+      </c>
+      <c r="F4" s="38" t="s">
+        <v>223</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="H4" s="38" t="s">
+        <v>224</v>
+      </c>
+      <c r="I4" s="7">
+        <v>4</v>
+      </c>
+      <c r="J4" s="38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="168" customHeight="1">
       <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="16"/>
+      <c r="B5" s="15"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="19"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="18"/>
       <c r="I5" s="7"/>
-      <c r="J5" s="19"/>
+      <c r="J5" s="18"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="9">
@@ -3364,35 +2772,33 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="E6" s="7"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="21"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="19"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="F7" s="18"/>
+      <c r="F7" s="17"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="F8" s="20"/>
+      <c r="F8" s="17"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="F9" s="18"/>
+      <c r="F9" s="17"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/2584cd05cdc1b59d1bc66b29b55425e534f5034d" tooltip="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/2584cd05cdc1b59d1bc66b29b55425e534f5034d"/>
+    <hyperlink ref="G2" r:id="rId1" tooltip="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/2584cd05cdc1b59d1bc66b29b55425e534f5034d" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
@@ -3414,7 +2820,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="3" ht="26.4" customHeight="1" spans="1:2">
+    <row r="3" spans="1:2" ht="26.4" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>37</v>
       </c>
@@ -3422,7 +2828,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="4" ht="26.4" customHeight="1" spans="1:2">
+    <row r="4" spans="1:2" ht="26.4" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>38</v>
       </c>
@@ -3438,7 +2844,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="6" ht="26.4" customHeight="1" spans="1:2">
+    <row r="6" spans="1:2" ht="26.4" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>40</v>
       </c>
@@ -3446,7 +2852,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="7" ht="26.4" customHeight="1" spans="1:2">
+    <row r="7" spans="1:2" ht="26.4" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
@@ -3454,7 +2860,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="8" ht="39.6" customHeight="1" spans="1:2">
+    <row r="8" spans="1:2" ht="39.6" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>42</v>
       </c>
@@ -3462,7 +2868,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="9" ht="26.4" customHeight="1" spans="1:2">
+    <row r="9" spans="1:2" ht="26.4" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>43</v>
       </c>
@@ -3478,7 +2884,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="11" ht="26.4" customHeight="1" spans="1:2">
+    <row r="11" spans="1:2" ht="26.4" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>45</v>
       </c>
@@ -3488,6 +2894,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/docs/PRJ301_SE20C_GROUP4 .xlsx
+++ b/docs/PRJ301_SE20C_GROUP4 .xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tuong Vy\Documents\GitHub\PRJ---24-7-LLM-Tutor\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PRJ301\PRJ---24-7-LLM-Tutor\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9618B291-CC9D-4A77-9D83-13864DCC7367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75BC1F40-7902-45CD-99AD-1FDA2654A82C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="233">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -774,12 +774,30 @@
   <si>
     <t>https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/3901ac5418d96497394a4d6afe77c7064be455f6</t>
   </si>
+  <si>
+    <t>Integrate the Chat UI and personalized Learning Path UI with the real backend, including role-based navigation, chat history, and JSON/AJAX communication.</t>
+  </si>
+  <si>
+    <t>Google Antigravity IDE, Gemini, ChatGPT</t>
+  </si>
+  <si>
+    <t>Integrated chat.jsp with the ChatServlet/AiTutorService backend and connected the learning-path page to LearningPathServlet. Added role-aware menu/navigation, chat history display, and asynchronous JSON/AJAX requests so the UI can communicate with backend services without a full page reload.</t>
+  </si>
+  <si>
+    <t>Reviewed the JSP-to-Servlet routes and JSON response format; aligned the Chat and Learning Path pages with the existing MVC structure. Checked role-based menu visibility and the chat-to-learning-path flow, and kept API credentials and AI-provider calls on the server side. Final validation should cover student, lecturer, and admin accounts.</t>
+  </si>
+  <si>
+    <t>1 chat.jsp; 1 Learning Path page; role-based navigation; chat history; JSON/AJAX communication between UI and backend.</t>
+  </si>
+  <si>
+    <t>UI routes may not match Servlet mappings; JSON parsing or network failures can leave the interface without feedback; chat history must be scoped to the authenticated student; menu visibility alone is not sufficient authorization, so backend role checks must also be verified.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -864,6 +882,11 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -966,7 +989,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1064,19 +1087,22 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1389,99 +1415,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.05" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="35"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="36"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="36"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="36"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="36"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="36"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="36"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="36">
+      <c r="B8" s="34">
         <v>4</v>
       </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="36"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="36"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="35"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="36"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
@@ -2723,31 +2749,31 @@
       <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="33" t="s">
         <v>196</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="33" t="s">
         <v>221</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="E4" s="38" t="s">
+      <c r="E4" s="33" t="s">
         <v>222</v>
       </c>
-      <c r="F4" s="38" t="s">
+      <c r="F4" s="33" t="s">
         <v>223</v>
       </c>
       <c r="G4" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="H4" s="38" t="s">
+      <c r="H4" s="33" t="s">
         <v>224</v>
       </c>
       <c r="I4" s="7">
         <v>4</v>
       </c>
-      <c r="J4" s="38" t="s">
+      <c r="J4" s="33" t="s">
         <v>225</v>
       </c>
     </row>
@@ -2755,15 +2781,31 @@
       <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="17"/>
+      <c r="B5" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>230</v>
+      </c>
       <c r="G5" s="14"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="18"/>
+      <c r="H5" s="39" t="s">
+        <v>231</v>
+      </c>
+      <c r="I5" s="39">
+        <v>5</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="9">

--- a/docs/PRJ301_SE20C_GROUP4 .xlsx
+++ b/docs/PRJ301_SE20C_GROUP4 .xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PRJ301\PRJ---24-7-LLM-Tutor\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PRJ---24-7-LLM-Tutor\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75BC1F40-7902-45CD-99AD-1FDA2654A82C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE37CC5-F498-4831-8EA2-C50C293C13FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="241">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -792,6 +792,30 @@
   <si>
     <t>UI routes may not match Servlet mappings; JSON parsing or network failures can leave the interface without feedback; chat history must be scoped to the authenticated student; menu visibility alone is not sufficient authorization, so backend role checks must also be verified.</t>
   </si>
+  <si>
+    <t>https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/2584cd0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementation &amp; Testing	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Develop AI chat history management: save messages to Tutor_Sessions &amp; Tutor_Messages, retrieve top 20 recent sessions, delete sessions, and enforce session ownership control.	</t>
+  </si>
+  <si>
+    <t>ChatGPT / GitHub Copilot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated code for 2 Models, 1 DAO with session/message CRUD methods, and test case templates.	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hardened SQL queries with PreparedStatement, enforced ownership checks via WHERE session_id = ? AND user_id = ? to prevent IDOR vulnerabilities (preventing unauthorized access to others' chats), and configured ON DELETE CASCADE.	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 DAO, 2 Models, maximum 20 recent sessions per user.	</t>
+  </si>
+  <si>
+    <t>AI tended to omit userId checks in delete and get operations, relying solely on sessionId, which could expose private conversations to other users. Required manual validation and refactoring.</t>
+  </si>
 </sst>
 </file>
 
@@ -803,6 +827,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -872,13 +903,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
@@ -887,7 +911,7 @@
     <font>
       <sz val="11"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -985,37 +1009,37 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1024,85 +1048,91 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1415,99 +1445,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.05" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="36"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="37"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="37"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="37"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="37"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="37"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="37"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="35">
         <v>4</v>
       </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="37"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="37"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="36"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="37"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
@@ -2796,29 +2826,50 @@
       <c r="F5" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="G5" s="14"/>
-      <c r="H5" s="39" t="s">
+      <c r="G5" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="H5" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="I5" s="39">
+      <c r="I5" s="34">
         <v>5</v>
       </c>
       <c r="J5" s="11" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" ht="96.6">
       <c r="A6" s="9">
         <v>5</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
+      <c r="B6" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="D6" s="40" t="s">
+        <v>236</v>
+      </c>
+      <c r="E6" s="40" t="s">
+        <v>237</v>
+      </c>
+      <c r="F6" s="41" t="s">
+        <v>238</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="7" spans="1:10">
       <c r="F7" s="17"/>
@@ -2832,6 +2883,8 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" tooltip="https://github.com/trieuvy2006/PRJ---24-7-LLM-Tutor/commit/2584cd05cdc1b59d1bc66b29b55425e534f5034d" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
+    <hyperlink ref="G5" r:id="rId2" xr:uid="{AAF13160-8905-44AB-B992-CCAB5479A1DF}"/>
+    <hyperlink ref="G6" r:id="rId3" xr:uid="{D712FFBF-3A47-4673-85A6-B9DFE0ED42D8}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
